--- a/t1_confection/A1_Outputs/A1_Outputs_B_Optimised_VRE/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_B_Optimised_VRE/A-O_AR_Projections_COMPLETED.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4415" uniqueCount="1254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4175" uniqueCount="1254">
   <si>
     <t>Mode.Operation</t>
   </si>
@@ -18708,7 +18708,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AH551"/>
+  <dimension ref="A1:AH503"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:34">
@@ -71020,4998 +71020,6 @@
         <v>0.95</v>
       </c>
       <c r="AH503">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="504" spans="1:34">
-      <c r="A504">
-        <v>1</v>
-      </c>
-      <c r="B504" t="s">
-        <v>750</v>
-      </c>
-      <c r="C504" t="s">
-        <v>925</v>
-      </c>
-      <c r="D504" t="s">
-        <v>395</v>
-      </c>
-      <c r="E504" t="s">
-        <v>534</v>
-      </c>
-      <c r="F504" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G504">
-        <v>1</v>
-      </c>
-      <c r="H504">
-        <v>1</v>
-      </c>
-      <c r="I504">
-        <v>1</v>
-      </c>
-      <c r="J504">
-        <v>1</v>
-      </c>
-      <c r="K504">
-        <v>1</v>
-      </c>
-      <c r="L504">
-        <v>1</v>
-      </c>
-      <c r="M504">
-        <v>1</v>
-      </c>
-      <c r="N504">
-        <v>1</v>
-      </c>
-      <c r="O504">
-        <v>1</v>
-      </c>
-      <c r="P504">
-        <v>1</v>
-      </c>
-      <c r="Q504">
-        <v>1</v>
-      </c>
-      <c r="R504">
-        <v>1</v>
-      </c>
-      <c r="S504">
-        <v>1</v>
-      </c>
-      <c r="T504">
-        <v>1</v>
-      </c>
-      <c r="U504">
-        <v>1</v>
-      </c>
-      <c r="V504">
-        <v>1</v>
-      </c>
-      <c r="W504">
-        <v>1</v>
-      </c>
-      <c r="X504">
-        <v>1</v>
-      </c>
-      <c r="Y504">
-        <v>1</v>
-      </c>
-      <c r="Z504">
-        <v>1</v>
-      </c>
-      <c r="AA504">
-        <v>1</v>
-      </c>
-      <c r="AB504">
-        <v>1</v>
-      </c>
-      <c r="AC504">
-        <v>1</v>
-      </c>
-      <c r="AD504">
-        <v>1</v>
-      </c>
-      <c r="AE504">
-        <v>1</v>
-      </c>
-      <c r="AF504">
-        <v>1</v>
-      </c>
-      <c r="AG504">
-        <v>1</v>
-      </c>
-      <c r="AH504">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="505" spans="1:34">
-      <c r="A505">
-        <v>1</v>
-      </c>
-      <c r="B505" t="s">
-        <v>750</v>
-      </c>
-      <c r="C505" t="s">
-        <v>925</v>
-      </c>
-      <c r="D505" t="s">
-        <v>954</v>
-      </c>
-      <c r="E505" t="s">
-        <v>994</v>
-      </c>
-      <c r="F505" t="s">
-        <v>590</v>
-      </c>
-      <c r="G505">
-        <v>1</v>
-      </c>
-      <c r="H505">
-        <v>1</v>
-      </c>
-      <c r="I505">
-        <v>1</v>
-      </c>
-      <c r="J505">
-        <v>1</v>
-      </c>
-      <c r="K505">
-        <v>1</v>
-      </c>
-      <c r="L505">
-        <v>1</v>
-      </c>
-      <c r="M505">
-        <v>1</v>
-      </c>
-      <c r="N505">
-        <v>1</v>
-      </c>
-      <c r="O505">
-        <v>1</v>
-      </c>
-      <c r="P505">
-        <v>1</v>
-      </c>
-      <c r="Q505">
-        <v>1</v>
-      </c>
-      <c r="R505">
-        <v>1</v>
-      </c>
-      <c r="S505">
-        <v>1</v>
-      </c>
-      <c r="T505">
-        <v>1</v>
-      </c>
-      <c r="U505">
-        <v>1</v>
-      </c>
-      <c r="V505">
-        <v>1</v>
-      </c>
-      <c r="W505">
-        <v>1</v>
-      </c>
-      <c r="X505">
-        <v>1</v>
-      </c>
-      <c r="Y505">
-        <v>1</v>
-      </c>
-      <c r="Z505">
-        <v>1</v>
-      </c>
-      <c r="AA505">
-        <v>1</v>
-      </c>
-      <c r="AB505">
-        <v>1</v>
-      </c>
-      <c r="AC505">
-        <v>1</v>
-      </c>
-      <c r="AD505">
-        <v>1</v>
-      </c>
-      <c r="AE505">
-        <v>1</v>
-      </c>
-      <c r="AF505">
-        <v>1</v>
-      </c>
-      <c r="AG505">
-        <v>1</v>
-      </c>
-      <c r="AH505">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="506" spans="1:34">
-      <c r="A506">
-        <v>1</v>
-      </c>
-      <c r="B506" t="s">
-        <v>751</v>
-      </c>
-      <c r="C506" t="s">
-        <v>926</v>
-      </c>
-      <c r="D506" t="s">
-        <v>328</v>
-      </c>
-      <c r="E506" t="s">
-        <v>467</v>
-      </c>
-      <c r="F506" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G506">
-        <v>2.3376</v>
-      </c>
-      <c r="H506">
-        <v>2.3376</v>
-      </c>
-      <c r="I506">
-        <v>2.3376</v>
-      </c>
-      <c r="J506">
-        <v>2.3376</v>
-      </c>
-      <c r="K506">
-        <v>2.3376</v>
-      </c>
-      <c r="L506">
-        <v>2.3376</v>
-      </c>
-      <c r="M506">
-        <v>2.3376</v>
-      </c>
-      <c r="N506">
-        <v>2.3376</v>
-      </c>
-      <c r="O506">
-        <v>2.3376</v>
-      </c>
-      <c r="P506">
-        <v>2.3376</v>
-      </c>
-      <c r="Q506">
-        <v>2.3376</v>
-      </c>
-      <c r="R506">
-        <v>2.3376</v>
-      </c>
-      <c r="S506">
-        <v>2.3376</v>
-      </c>
-      <c r="T506">
-        <v>2.3376</v>
-      </c>
-      <c r="U506">
-        <v>2.3376</v>
-      </c>
-      <c r="V506">
-        <v>2.3376</v>
-      </c>
-      <c r="W506">
-        <v>2.3376</v>
-      </c>
-      <c r="X506">
-        <v>2.3376</v>
-      </c>
-      <c r="Y506">
-        <v>2.3376</v>
-      </c>
-      <c r="Z506">
-        <v>2.3376</v>
-      </c>
-      <c r="AA506">
-        <v>2.3376</v>
-      </c>
-      <c r="AB506">
-        <v>2.3376</v>
-      </c>
-      <c r="AC506">
-        <v>2.3376</v>
-      </c>
-      <c r="AD506">
-        <v>2.3376</v>
-      </c>
-      <c r="AE506">
-        <v>2.3376</v>
-      </c>
-      <c r="AF506">
-        <v>2.3376</v>
-      </c>
-      <c r="AG506">
-        <v>2.3376</v>
-      </c>
-      <c r="AH506">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="507" spans="1:34">
-      <c r="A507">
-        <v>2</v>
-      </c>
-      <c r="B507" t="s">
-        <v>751</v>
-      </c>
-      <c r="C507" t="s">
-        <v>926</v>
-      </c>
-      <c r="D507" t="s">
-        <v>329</v>
-      </c>
-      <c r="E507" t="s">
-        <v>468</v>
-      </c>
-      <c r="F507" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G507">
-        <v>2.3376</v>
-      </c>
-      <c r="H507">
-        <v>2.3376</v>
-      </c>
-      <c r="I507">
-        <v>2.3376</v>
-      </c>
-      <c r="J507">
-        <v>2.3376</v>
-      </c>
-      <c r="K507">
-        <v>2.3376</v>
-      </c>
-      <c r="L507">
-        <v>2.3376</v>
-      </c>
-      <c r="M507">
-        <v>2.3376</v>
-      </c>
-      <c r="N507">
-        <v>2.3376</v>
-      </c>
-      <c r="O507">
-        <v>2.3376</v>
-      </c>
-      <c r="P507">
-        <v>2.3376</v>
-      </c>
-      <c r="Q507">
-        <v>2.3376</v>
-      </c>
-      <c r="R507">
-        <v>2.3376</v>
-      </c>
-      <c r="S507">
-        <v>2.3376</v>
-      </c>
-      <c r="T507">
-        <v>2.3376</v>
-      </c>
-      <c r="U507">
-        <v>2.3376</v>
-      </c>
-      <c r="V507">
-        <v>2.3376</v>
-      </c>
-      <c r="W507">
-        <v>2.3376</v>
-      </c>
-      <c r="X507">
-        <v>2.3376</v>
-      </c>
-      <c r="Y507">
-        <v>2.3376</v>
-      </c>
-      <c r="Z507">
-        <v>2.3376</v>
-      </c>
-      <c r="AA507">
-        <v>2.3376</v>
-      </c>
-      <c r="AB507">
-        <v>2.3376</v>
-      </c>
-      <c r="AC507">
-        <v>2.3376</v>
-      </c>
-      <c r="AD507">
-        <v>2.3376</v>
-      </c>
-      <c r="AE507">
-        <v>2.3376</v>
-      </c>
-      <c r="AF507">
-        <v>2.3376</v>
-      </c>
-      <c r="AG507">
-        <v>2.3376</v>
-      </c>
-      <c r="AH507">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="508" spans="1:34">
-      <c r="A508">
-        <v>1</v>
-      </c>
-      <c r="B508" t="s">
-        <v>751</v>
-      </c>
-      <c r="C508" t="s">
-        <v>926</v>
-      </c>
-      <c r="D508" t="s">
-        <v>941</v>
-      </c>
-      <c r="E508" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F508" t="s">
-        <v>590</v>
-      </c>
-      <c r="G508">
-        <v>1</v>
-      </c>
-      <c r="H508">
-        <v>1</v>
-      </c>
-      <c r="I508">
-        <v>1</v>
-      </c>
-      <c r="J508">
-        <v>1</v>
-      </c>
-      <c r="K508">
-        <v>1</v>
-      </c>
-      <c r="L508">
-        <v>1</v>
-      </c>
-      <c r="M508">
-        <v>1</v>
-      </c>
-      <c r="N508">
-        <v>1</v>
-      </c>
-      <c r="O508">
-        <v>1</v>
-      </c>
-      <c r="P508">
-        <v>1</v>
-      </c>
-      <c r="Q508">
-        <v>1</v>
-      </c>
-      <c r="R508">
-        <v>1</v>
-      </c>
-      <c r="S508">
-        <v>1</v>
-      </c>
-      <c r="T508">
-        <v>1</v>
-      </c>
-      <c r="U508">
-        <v>1</v>
-      </c>
-      <c r="V508">
-        <v>1</v>
-      </c>
-      <c r="W508">
-        <v>1</v>
-      </c>
-      <c r="X508">
-        <v>1</v>
-      </c>
-      <c r="Y508">
-        <v>1</v>
-      </c>
-      <c r="Z508">
-        <v>1</v>
-      </c>
-      <c r="AA508">
-        <v>1</v>
-      </c>
-      <c r="AB508">
-        <v>1</v>
-      </c>
-      <c r="AC508">
-        <v>1</v>
-      </c>
-      <c r="AD508">
-        <v>1</v>
-      </c>
-      <c r="AE508">
-        <v>1</v>
-      </c>
-      <c r="AF508">
-        <v>1</v>
-      </c>
-      <c r="AG508">
-        <v>1</v>
-      </c>
-      <c r="AH508">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="509" spans="1:34">
-      <c r="A509">
-        <v>2</v>
-      </c>
-      <c r="B509" t="s">
-        <v>751</v>
-      </c>
-      <c r="C509" t="s">
-        <v>926</v>
-      </c>
-      <c r="D509" t="s">
-        <v>941</v>
-      </c>
-      <c r="E509" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F509" t="s">
-        <v>590</v>
-      </c>
-      <c r="G509">
-        <v>1</v>
-      </c>
-      <c r="H509">
-        <v>1</v>
-      </c>
-      <c r="I509">
-        <v>1</v>
-      </c>
-      <c r="J509">
-        <v>1</v>
-      </c>
-      <c r="K509">
-        <v>1</v>
-      </c>
-      <c r="L509">
-        <v>1</v>
-      </c>
-      <c r="M509">
-        <v>1</v>
-      </c>
-      <c r="N509">
-        <v>1</v>
-      </c>
-      <c r="O509">
-        <v>1</v>
-      </c>
-      <c r="P509">
-        <v>1</v>
-      </c>
-      <c r="Q509">
-        <v>1</v>
-      </c>
-      <c r="R509">
-        <v>1</v>
-      </c>
-      <c r="S509">
-        <v>1</v>
-      </c>
-      <c r="T509">
-        <v>1</v>
-      </c>
-      <c r="U509">
-        <v>1</v>
-      </c>
-      <c r="V509">
-        <v>1</v>
-      </c>
-      <c r="W509">
-        <v>1</v>
-      </c>
-      <c r="X509">
-        <v>1</v>
-      </c>
-      <c r="Y509">
-        <v>1</v>
-      </c>
-      <c r="Z509">
-        <v>1</v>
-      </c>
-      <c r="AA509">
-        <v>1</v>
-      </c>
-      <c r="AB509">
-        <v>1</v>
-      </c>
-      <c r="AC509">
-        <v>1</v>
-      </c>
-      <c r="AD509">
-        <v>1</v>
-      </c>
-      <c r="AE509">
-        <v>1</v>
-      </c>
-      <c r="AF509">
-        <v>1</v>
-      </c>
-      <c r="AG509">
-        <v>1</v>
-      </c>
-      <c r="AH509">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="510" spans="1:34">
-      <c r="A510">
-        <v>1</v>
-      </c>
-      <c r="B510" t="s">
-        <v>752</v>
-      </c>
-      <c r="C510" t="s">
-        <v>927</v>
-      </c>
-      <c r="D510" t="s">
-        <v>328</v>
-      </c>
-      <c r="E510" t="s">
-        <v>467</v>
-      </c>
-      <c r="F510" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G510">
-        <v>2.3376</v>
-      </c>
-      <c r="H510">
-        <v>2.3376</v>
-      </c>
-      <c r="I510">
-        <v>2.3376</v>
-      </c>
-      <c r="J510">
-        <v>2.3376</v>
-      </c>
-      <c r="K510">
-        <v>2.3376</v>
-      </c>
-      <c r="L510">
-        <v>2.3376</v>
-      </c>
-      <c r="M510">
-        <v>2.3376</v>
-      </c>
-      <c r="N510">
-        <v>2.3376</v>
-      </c>
-      <c r="O510">
-        <v>2.3376</v>
-      </c>
-      <c r="P510">
-        <v>2.3376</v>
-      </c>
-      <c r="Q510">
-        <v>2.3376</v>
-      </c>
-      <c r="R510">
-        <v>2.3376</v>
-      </c>
-      <c r="S510">
-        <v>2.3376</v>
-      </c>
-      <c r="T510">
-        <v>2.3376</v>
-      </c>
-      <c r="U510">
-        <v>2.3376</v>
-      </c>
-      <c r="V510">
-        <v>2.3376</v>
-      </c>
-      <c r="W510">
-        <v>2.3376</v>
-      </c>
-      <c r="X510">
-        <v>2.3376</v>
-      </c>
-      <c r="Y510">
-        <v>2.3376</v>
-      </c>
-      <c r="Z510">
-        <v>2.3376</v>
-      </c>
-      <c r="AA510">
-        <v>2.3376</v>
-      </c>
-      <c r="AB510">
-        <v>2.3376</v>
-      </c>
-      <c r="AC510">
-        <v>2.3376</v>
-      </c>
-      <c r="AD510">
-        <v>2.3376</v>
-      </c>
-      <c r="AE510">
-        <v>2.3376</v>
-      </c>
-      <c r="AF510">
-        <v>2.3376</v>
-      </c>
-      <c r="AG510">
-        <v>2.3376</v>
-      </c>
-      <c r="AH510">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="511" spans="1:34">
-      <c r="A511">
-        <v>2</v>
-      </c>
-      <c r="B511" t="s">
-        <v>752</v>
-      </c>
-      <c r="C511" t="s">
-        <v>927</v>
-      </c>
-      <c r="D511" t="s">
-        <v>329</v>
-      </c>
-      <c r="E511" t="s">
-        <v>468</v>
-      </c>
-      <c r="F511" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G511">
-        <v>2.3376</v>
-      </c>
-      <c r="H511">
-        <v>2.3376</v>
-      </c>
-      <c r="I511">
-        <v>2.3376</v>
-      </c>
-      <c r="J511">
-        <v>2.3376</v>
-      </c>
-      <c r="K511">
-        <v>2.3376</v>
-      </c>
-      <c r="L511">
-        <v>2.3376</v>
-      </c>
-      <c r="M511">
-        <v>2.3376</v>
-      </c>
-      <c r="N511">
-        <v>2.3376</v>
-      </c>
-      <c r="O511">
-        <v>2.3376</v>
-      </c>
-      <c r="P511">
-        <v>2.3376</v>
-      </c>
-      <c r="Q511">
-        <v>2.3376</v>
-      </c>
-      <c r="R511">
-        <v>2.3376</v>
-      </c>
-      <c r="S511">
-        <v>2.3376</v>
-      </c>
-      <c r="T511">
-        <v>2.3376</v>
-      </c>
-      <c r="U511">
-        <v>2.3376</v>
-      </c>
-      <c r="V511">
-        <v>2.3376</v>
-      </c>
-      <c r="W511">
-        <v>2.3376</v>
-      </c>
-      <c r="X511">
-        <v>2.3376</v>
-      </c>
-      <c r="Y511">
-        <v>2.3376</v>
-      </c>
-      <c r="Z511">
-        <v>2.3376</v>
-      </c>
-      <c r="AA511">
-        <v>2.3376</v>
-      </c>
-      <c r="AB511">
-        <v>2.3376</v>
-      </c>
-      <c r="AC511">
-        <v>2.3376</v>
-      </c>
-      <c r="AD511">
-        <v>2.3376</v>
-      </c>
-      <c r="AE511">
-        <v>2.3376</v>
-      </c>
-      <c r="AF511">
-        <v>2.3376</v>
-      </c>
-      <c r="AG511">
-        <v>2.3376</v>
-      </c>
-      <c r="AH511">
-        <v>2.3376</v>
-      </c>
-    </row>
-    <row r="512" spans="1:34">
-      <c r="A512">
-        <v>1</v>
-      </c>
-      <c r="B512" t="s">
-        <v>752</v>
-      </c>
-      <c r="C512" t="s">
-        <v>927</v>
-      </c>
-      <c r="D512" t="s">
-        <v>949</v>
-      </c>
-      <c r="E512" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F512" t="s">
-        <v>590</v>
-      </c>
-      <c r="G512">
-        <v>1</v>
-      </c>
-      <c r="H512">
-        <v>1</v>
-      </c>
-      <c r="I512">
-        <v>1</v>
-      </c>
-      <c r="J512">
-        <v>1</v>
-      </c>
-      <c r="K512">
-        <v>1</v>
-      </c>
-      <c r="L512">
-        <v>1</v>
-      </c>
-      <c r="M512">
-        <v>1</v>
-      </c>
-      <c r="N512">
-        <v>1</v>
-      </c>
-      <c r="O512">
-        <v>1</v>
-      </c>
-      <c r="P512">
-        <v>1</v>
-      </c>
-      <c r="Q512">
-        <v>1</v>
-      </c>
-      <c r="R512">
-        <v>1</v>
-      </c>
-      <c r="S512">
-        <v>1</v>
-      </c>
-      <c r="T512">
-        <v>1</v>
-      </c>
-      <c r="U512">
-        <v>1</v>
-      </c>
-      <c r="V512">
-        <v>1</v>
-      </c>
-      <c r="W512">
-        <v>1</v>
-      </c>
-      <c r="X512">
-        <v>1</v>
-      </c>
-      <c r="Y512">
-        <v>1</v>
-      </c>
-      <c r="Z512">
-        <v>1</v>
-      </c>
-      <c r="AA512">
-        <v>1</v>
-      </c>
-      <c r="AB512">
-        <v>1</v>
-      </c>
-      <c r="AC512">
-        <v>1</v>
-      </c>
-      <c r="AD512">
-        <v>1</v>
-      </c>
-      <c r="AE512">
-        <v>1</v>
-      </c>
-      <c r="AF512">
-        <v>1</v>
-      </c>
-      <c r="AG512">
-        <v>1</v>
-      </c>
-      <c r="AH512">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="513" spans="1:34">
-      <c r="A513">
-        <v>2</v>
-      </c>
-      <c r="B513" t="s">
-        <v>752</v>
-      </c>
-      <c r="C513" t="s">
-        <v>927</v>
-      </c>
-      <c r="D513" t="s">
-        <v>949</v>
-      </c>
-      <c r="E513" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F513" t="s">
-        <v>590</v>
-      </c>
-      <c r="G513">
-        <v>1</v>
-      </c>
-      <c r="H513">
-        <v>1</v>
-      </c>
-      <c r="I513">
-        <v>1</v>
-      </c>
-      <c r="J513">
-        <v>1</v>
-      </c>
-      <c r="K513">
-        <v>1</v>
-      </c>
-      <c r="L513">
-        <v>1</v>
-      </c>
-      <c r="M513">
-        <v>1</v>
-      </c>
-      <c r="N513">
-        <v>1</v>
-      </c>
-      <c r="O513">
-        <v>1</v>
-      </c>
-      <c r="P513">
-        <v>1</v>
-      </c>
-      <c r="Q513">
-        <v>1</v>
-      </c>
-      <c r="R513">
-        <v>1</v>
-      </c>
-      <c r="S513">
-        <v>1</v>
-      </c>
-      <c r="T513">
-        <v>1</v>
-      </c>
-      <c r="U513">
-        <v>1</v>
-      </c>
-      <c r="V513">
-        <v>1</v>
-      </c>
-      <c r="W513">
-        <v>1</v>
-      </c>
-      <c r="X513">
-        <v>1</v>
-      </c>
-      <c r="Y513">
-        <v>1</v>
-      </c>
-      <c r="Z513">
-        <v>1</v>
-      </c>
-      <c r="AA513">
-        <v>1</v>
-      </c>
-      <c r="AB513">
-        <v>1</v>
-      </c>
-      <c r="AC513">
-        <v>1</v>
-      </c>
-      <c r="AD513">
-        <v>1</v>
-      </c>
-      <c r="AE513">
-        <v>1</v>
-      </c>
-      <c r="AF513">
-        <v>1</v>
-      </c>
-      <c r="AG513">
-        <v>1</v>
-      </c>
-      <c r="AH513">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="514" spans="1:34">
-      <c r="A514">
-        <v>1</v>
-      </c>
-      <c r="B514" t="s">
-        <v>753</v>
-      </c>
-      <c r="C514" t="s">
-        <v>928</v>
-      </c>
-      <c r="D514" t="s">
-        <v>333</v>
-      </c>
-      <c r="E514" t="s">
-        <v>472</v>
-      </c>
-      <c r="F514" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G514">
-        <v>2.8571</v>
-      </c>
-      <c r="H514">
-        <v>2.8571</v>
-      </c>
-      <c r="I514">
-        <v>2.8571</v>
-      </c>
-      <c r="J514">
-        <v>2.8571</v>
-      </c>
-      <c r="K514">
-        <v>2.8571</v>
-      </c>
-      <c r="L514">
-        <v>2.8571</v>
-      </c>
-      <c r="M514">
-        <v>2.8571</v>
-      </c>
-      <c r="N514">
-        <v>2.8571</v>
-      </c>
-      <c r="O514">
-        <v>2.8571</v>
-      </c>
-      <c r="P514">
-        <v>2.8571</v>
-      </c>
-      <c r="Q514">
-        <v>2.8571</v>
-      </c>
-      <c r="R514">
-        <v>2.8571</v>
-      </c>
-      <c r="S514">
-        <v>2.8571</v>
-      </c>
-      <c r="T514">
-        <v>2.8571</v>
-      </c>
-      <c r="U514">
-        <v>2.8571</v>
-      </c>
-      <c r="V514">
-        <v>2.8571</v>
-      </c>
-      <c r="W514">
-        <v>2.8571</v>
-      </c>
-      <c r="X514">
-        <v>2.8571</v>
-      </c>
-      <c r="Y514">
-        <v>2.8571</v>
-      </c>
-      <c r="Z514">
-        <v>2.8571</v>
-      </c>
-      <c r="AA514">
-        <v>2.8571</v>
-      </c>
-      <c r="AB514">
-        <v>2.8571</v>
-      </c>
-      <c r="AC514">
-        <v>2.8571</v>
-      </c>
-      <c r="AD514">
-        <v>2.8571</v>
-      </c>
-      <c r="AE514">
-        <v>2.8571</v>
-      </c>
-      <c r="AF514">
-        <v>2.8571</v>
-      </c>
-      <c r="AG514">
-        <v>2.8571</v>
-      </c>
-      <c r="AH514">
-        <v>2.8571</v>
-      </c>
-    </row>
-    <row r="515" spans="1:34">
-      <c r="A515">
-        <v>2</v>
-      </c>
-      <c r="B515" t="s">
-        <v>753</v>
-      </c>
-      <c r="C515" t="s">
-        <v>928</v>
-      </c>
-      <c r="D515" t="s">
-        <v>336</v>
-      </c>
-      <c r="E515" t="s">
-        <v>475</v>
-      </c>
-      <c r="F515" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G515">
-        <v>2.8571</v>
-      </c>
-      <c r="H515">
-        <v>2.8571</v>
-      </c>
-      <c r="I515">
-        <v>2.8571</v>
-      </c>
-      <c r="J515">
-        <v>2.8571</v>
-      </c>
-      <c r="K515">
-        <v>2.8571</v>
-      </c>
-      <c r="L515">
-        <v>2.8571</v>
-      </c>
-      <c r="M515">
-        <v>2.8571</v>
-      </c>
-      <c r="N515">
-        <v>2.8571</v>
-      </c>
-      <c r="O515">
-        <v>2.8571</v>
-      </c>
-      <c r="P515">
-        <v>2.8571</v>
-      </c>
-      <c r="Q515">
-        <v>2.8571</v>
-      </c>
-      <c r="R515">
-        <v>2.8571</v>
-      </c>
-      <c r="S515">
-        <v>2.8571</v>
-      </c>
-      <c r="T515">
-        <v>2.8571</v>
-      </c>
-      <c r="U515">
-        <v>2.8571</v>
-      </c>
-      <c r="V515">
-        <v>2.8571</v>
-      </c>
-      <c r="W515">
-        <v>2.8571</v>
-      </c>
-      <c r="X515">
-        <v>2.8571</v>
-      </c>
-      <c r="Y515">
-        <v>2.8571</v>
-      </c>
-      <c r="Z515">
-        <v>2.8571</v>
-      </c>
-      <c r="AA515">
-        <v>2.8571</v>
-      </c>
-      <c r="AB515">
-        <v>2.8571</v>
-      </c>
-      <c r="AC515">
-        <v>2.8571</v>
-      </c>
-      <c r="AD515">
-        <v>2.8571</v>
-      </c>
-      <c r="AE515">
-        <v>2.8571</v>
-      </c>
-      <c r="AF515">
-        <v>2.8571</v>
-      </c>
-      <c r="AG515">
-        <v>2.8571</v>
-      </c>
-      <c r="AH515">
-        <v>2.8571</v>
-      </c>
-    </row>
-    <row r="516" spans="1:34">
-      <c r="A516">
-        <v>1</v>
-      </c>
-      <c r="B516" t="s">
-        <v>753</v>
-      </c>
-      <c r="C516" t="s">
-        <v>928</v>
-      </c>
-      <c r="D516" t="s">
-        <v>949</v>
-      </c>
-      <c r="E516" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F516" t="s">
-        <v>590</v>
-      </c>
-      <c r="G516">
-        <v>1</v>
-      </c>
-      <c r="H516">
-        <v>1</v>
-      </c>
-      <c r="I516">
-        <v>1</v>
-      </c>
-      <c r="J516">
-        <v>1</v>
-      </c>
-      <c r="K516">
-        <v>1</v>
-      </c>
-      <c r="L516">
-        <v>1</v>
-      </c>
-      <c r="M516">
-        <v>1</v>
-      </c>
-      <c r="N516">
-        <v>1</v>
-      </c>
-      <c r="O516">
-        <v>1</v>
-      </c>
-      <c r="P516">
-        <v>1</v>
-      </c>
-      <c r="Q516">
-        <v>1</v>
-      </c>
-      <c r="R516">
-        <v>1</v>
-      </c>
-      <c r="S516">
-        <v>1</v>
-      </c>
-      <c r="T516">
-        <v>1</v>
-      </c>
-      <c r="U516">
-        <v>1</v>
-      </c>
-      <c r="V516">
-        <v>1</v>
-      </c>
-      <c r="W516">
-        <v>1</v>
-      </c>
-      <c r="X516">
-        <v>1</v>
-      </c>
-      <c r="Y516">
-        <v>1</v>
-      </c>
-      <c r="Z516">
-        <v>1</v>
-      </c>
-      <c r="AA516">
-        <v>1</v>
-      </c>
-      <c r="AB516">
-        <v>1</v>
-      </c>
-      <c r="AC516">
-        <v>1</v>
-      </c>
-      <c r="AD516">
-        <v>1</v>
-      </c>
-      <c r="AE516">
-        <v>1</v>
-      </c>
-      <c r="AF516">
-        <v>1</v>
-      </c>
-      <c r="AG516">
-        <v>1</v>
-      </c>
-      <c r="AH516">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="517" spans="1:34">
-      <c r="A517">
-        <v>2</v>
-      </c>
-      <c r="B517" t="s">
-        <v>753</v>
-      </c>
-      <c r="C517" t="s">
-        <v>928</v>
-      </c>
-      <c r="D517" t="s">
-        <v>949</v>
-      </c>
-      <c r="E517" t="s">
-        <v>1022</v>
-      </c>
-      <c r="F517" t="s">
-        <v>590</v>
-      </c>
-      <c r="G517">
-        <v>1</v>
-      </c>
-      <c r="H517">
-        <v>1</v>
-      </c>
-      <c r="I517">
-        <v>1</v>
-      </c>
-      <c r="J517">
-        <v>1</v>
-      </c>
-      <c r="K517">
-        <v>1</v>
-      </c>
-      <c r="L517">
-        <v>1</v>
-      </c>
-      <c r="M517">
-        <v>1</v>
-      </c>
-      <c r="N517">
-        <v>1</v>
-      </c>
-      <c r="O517">
-        <v>1</v>
-      </c>
-      <c r="P517">
-        <v>1</v>
-      </c>
-      <c r="Q517">
-        <v>1</v>
-      </c>
-      <c r="R517">
-        <v>1</v>
-      </c>
-      <c r="S517">
-        <v>1</v>
-      </c>
-      <c r="T517">
-        <v>1</v>
-      </c>
-      <c r="U517">
-        <v>1</v>
-      </c>
-      <c r="V517">
-        <v>1</v>
-      </c>
-      <c r="W517">
-        <v>1</v>
-      </c>
-      <c r="X517">
-        <v>1</v>
-      </c>
-      <c r="Y517">
-        <v>1</v>
-      </c>
-      <c r="Z517">
-        <v>1</v>
-      </c>
-      <c r="AA517">
-        <v>1</v>
-      </c>
-      <c r="AB517">
-        <v>1</v>
-      </c>
-      <c r="AC517">
-        <v>1</v>
-      </c>
-      <c r="AD517">
-        <v>1</v>
-      </c>
-      <c r="AE517">
-        <v>1</v>
-      </c>
-      <c r="AF517">
-        <v>1</v>
-      </c>
-      <c r="AG517">
-        <v>1</v>
-      </c>
-      <c r="AH517">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="518" spans="1:34">
-      <c r="A518">
-        <v>1</v>
-      </c>
-      <c r="B518" t="s">
-        <v>754</v>
-      </c>
-      <c r="C518" t="s">
-        <v>929</v>
-      </c>
-      <c r="D518" t="s">
-        <v>333</v>
-      </c>
-      <c r="E518" t="s">
-        <v>472</v>
-      </c>
-      <c r="F518" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G518">
-        <v>2.88</v>
-      </c>
-      <c r="H518">
-        <v>2.88</v>
-      </c>
-      <c r="I518">
-        <v>2.88</v>
-      </c>
-      <c r="J518">
-        <v>2.88</v>
-      </c>
-      <c r="K518">
-        <v>2.88</v>
-      </c>
-      <c r="L518">
-        <v>2.88</v>
-      </c>
-      <c r="M518">
-        <v>2.88</v>
-      </c>
-      <c r="N518">
-        <v>2.88</v>
-      </c>
-      <c r="O518">
-        <v>2.88</v>
-      </c>
-      <c r="P518">
-        <v>2.88</v>
-      </c>
-      <c r="Q518">
-        <v>2.88</v>
-      </c>
-      <c r="R518">
-        <v>2.88</v>
-      </c>
-      <c r="S518">
-        <v>2.88</v>
-      </c>
-      <c r="T518">
-        <v>2.88</v>
-      </c>
-      <c r="U518">
-        <v>2.88</v>
-      </c>
-      <c r="V518">
-        <v>2.88</v>
-      </c>
-      <c r="W518">
-        <v>2.88</v>
-      </c>
-      <c r="X518">
-        <v>2.88</v>
-      </c>
-      <c r="Y518">
-        <v>2.88</v>
-      </c>
-      <c r="Z518">
-        <v>2.88</v>
-      </c>
-      <c r="AA518">
-        <v>2.88</v>
-      </c>
-      <c r="AB518">
-        <v>2.88</v>
-      </c>
-      <c r="AC518">
-        <v>2.88</v>
-      </c>
-      <c r="AD518">
-        <v>2.88</v>
-      </c>
-      <c r="AE518">
-        <v>2.88</v>
-      </c>
-      <c r="AF518">
-        <v>2.88</v>
-      </c>
-      <c r="AG518">
-        <v>2.88</v>
-      </c>
-      <c r="AH518">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="519" spans="1:34">
-      <c r="A519">
-        <v>2</v>
-      </c>
-      <c r="B519" t="s">
-        <v>754</v>
-      </c>
-      <c r="C519" t="s">
-        <v>929</v>
-      </c>
-      <c r="D519" t="s">
-        <v>336</v>
-      </c>
-      <c r="E519" t="s">
-        <v>475</v>
-      </c>
-      <c r="F519" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G519">
-        <v>2.88</v>
-      </c>
-      <c r="H519">
-        <v>2.88</v>
-      </c>
-      <c r="I519">
-        <v>2.88</v>
-      </c>
-      <c r="J519">
-        <v>2.88</v>
-      </c>
-      <c r="K519">
-        <v>2.88</v>
-      </c>
-      <c r="L519">
-        <v>2.88</v>
-      </c>
-      <c r="M519">
-        <v>2.88</v>
-      </c>
-      <c r="N519">
-        <v>2.88</v>
-      </c>
-      <c r="O519">
-        <v>2.88</v>
-      </c>
-      <c r="P519">
-        <v>2.88</v>
-      </c>
-      <c r="Q519">
-        <v>2.88</v>
-      </c>
-      <c r="R519">
-        <v>2.88</v>
-      </c>
-      <c r="S519">
-        <v>2.88</v>
-      </c>
-      <c r="T519">
-        <v>2.88</v>
-      </c>
-      <c r="U519">
-        <v>2.88</v>
-      </c>
-      <c r="V519">
-        <v>2.88</v>
-      </c>
-      <c r="W519">
-        <v>2.88</v>
-      </c>
-      <c r="X519">
-        <v>2.88</v>
-      </c>
-      <c r="Y519">
-        <v>2.88</v>
-      </c>
-      <c r="Z519">
-        <v>2.88</v>
-      </c>
-      <c r="AA519">
-        <v>2.88</v>
-      </c>
-      <c r="AB519">
-        <v>2.88</v>
-      </c>
-      <c r="AC519">
-        <v>2.88</v>
-      </c>
-      <c r="AD519">
-        <v>2.88</v>
-      </c>
-      <c r="AE519">
-        <v>2.88</v>
-      </c>
-      <c r="AF519">
-        <v>2.88</v>
-      </c>
-      <c r="AG519">
-        <v>2.88</v>
-      </c>
-      <c r="AH519">
-        <v>2.88</v>
-      </c>
-    </row>
-    <row r="520" spans="1:34">
-      <c r="A520">
-        <v>1</v>
-      </c>
-      <c r="B520" t="s">
-        <v>754</v>
-      </c>
-      <c r="C520" t="s">
-        <v>929</v>
-      </c>
-      <c r="D520" t="s">
-        <v>950</v>
-      </c>
-      <c r="E520" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F520" t="s">
-        <v>590</v>
-      </c>
-      <c r="G520">
-        <v>1</v>
-      </c>
-      <c r="H520">
-        <v>1</v>
-      </c>
-      <c r="I520">
-        <v>1</v>
-      </c>
-      <c r="J520">
-        <v>1</v>
-      </c>
-      <c r="K520">
-        <v>1</v>
-      </c>
-      <c r="L520">
-        <v>1</v>
-      </c>
-      <c r="M520">
-        <v>1</v>
-      </c>
-      <c r="N520">
-        <v>1</v>
-      </c>
-      <c r="O520">
-        <v>1</v>
-      </c>
-      <c r="P520">
-        <v>1</v>
-      </c>
-      <c r="Q520">
-        <v>1</v>
-      </c>
-      <c r="R520">
-        <v>1</v>
-      </c>
-      <c r="S520">
-        <v>1</v>
-      </c>
-      <c r="T520">
-        <v>1</v>
-      </c>
-      <c r="U520">
-        <v>1</v>
-      </c>
-      <c r="V520">
-        <v>1</v>
-      </c>
-      <c r="W520">
-        <v>1</v>
-      </c>
-      <c r="X520">
-        <v>1</v>
-      </c>
-      <c r="Y520">
-        <v>1</v>
-      </c>
-      <c r="Z520">
-        <v>1</v>
-      </c>
-      <c r="AA520">
-        <v>1</v>
-      </c>
-      <c r="AB520">
-        <v>1</v>
-      </c>
-      <c r="AC520">
-        <v>1</v>
-      </c>
-      <c r="AD520">
-        <v>1</v>
-      </c>
-      <c r="AE520">
-        <v>1</v>
-      </c>
-      <c r="AF520">
-        <v>1</v>
-      </c>
-      <c r="AG520">
-        <v>1</v>
-      </c>
-      <c r="AH520">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="521" spans="1:34">
-      <c r="A521">
-        <v>2</v>
-      </c>
-      <c r="B521" t="s">
-        <v>754</v>
-      </c>
-      <c r="C521" t="s">
-        <v>929</v>
-      </c>
-      <c r="D521" t="s">
-        <v>950</v>
-      </c>
-      <c r="E521" t="s">
-        <v>1023</v>
-      </c>
-      <c r="F521" t="s">
-        <v>590</v>
-      </c>
-      <c r="G521">
-        <v>1</v>
-      </c>
-      <c r="H521">
-        <v>1</v>
-      </c>
-      <c r="I521">
-        <v>1</v>
-      </c>
-      <c r="J521">
-        <v>1</v>
-      </c>
-      <c r="K521">
-        <v>1</v>
-      </c>
-      <c r="L521">
-        <v>1</v>
-      </c>
-      <c r="M521">
-        <v>1</v>
-      </c>
-      <c r="N521">
-        <v>1</v>
-      </c>
-      <c r="O521">
-        <v>1</v>
-      </c>
-      <c r="P521">
-        <v>1</v>
-      </c>
-      <c r="Q521">
-        <v>1</v>
-      </c>
-      <c r="R521">
-        <v>1</v>
-      </c>
-      <c r="S521">
-        <v>1</v>
-      </c>
-      <c r="T521">
-        <v>1</v>
-      </c>
-      <c r="U521">
-        <v>1</v>
-      </c>
-      <c r="V521">
-        <v>1</v>
-      </c>
-      <c r="W521">
-        <v>1</v>
-      </c>
-      <c r="X521">
-        <v>1</v>
-      </c>
-      <c r="Y521">
-        <v>1</v>
-      </c>
-      <c r="Z521">
-        <v>1</v>
-      </c>
-      <c r="AA521">
-        <v>1</v>
-      </c>
-      <c r="AB521">
-        <v>1</v>
-      </c>
-      <c r="AC521">
-        <v>1</v>
-      </c>
-      <c r="AD521">
-        <v>1</v>
-      </c>
-      <c r="AE521">
-        <v>1</v>
-      </c>
-      <c r="AF521">
-        <v>1</v>
-      </c>
-      <c r="AG521">
-        <v>1</v>
-      </c>
-      <c r="AH521">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="522" spans="1:34">
-      <c r="A522">
-        <v>1</v>
-      </c>
-      <c r="B522" t="s">
-        <v>755</v>
-      </c>
-      <c r="C522" t="s">
-        <v>930</v>
-      </c>
-      <c r="D522" t="s">
-        <v>393</v>
-      </c>
-      <c r="E522" t="s">
-        <v>532</v>
-      </c>
-      <c r="F522" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G522">
-        <v>1</v>
-      </c>
-      <c r="H522">
-        <v>1</v>
-      </c>
-      <c r="I522">
-        <v>1</v>
-      </c>
-      <c r="J522">
-        <v>1</v>
-      </c>
-      <c r="K522">
-        <v>1</v>
-      </c>
-      <c r="L522">
-        <v>1</v>
-      </c>
-      <c r="M522">
-        <v>1</v>
-      </c>
-      <c r="N522">
-        <v>1</v>
-      </c>
-      <c r="O522">
-        <v>1</v>
-      </c>
-      <c r="P522">
-        <v>1</v>
-      </c>
-      <c r="Q522">
-        <v>1</v>
-      </c>
-      <c r="R522">
-        <v>1</v>
-      </c>
-      <c r="S522">
-        <v>1</v>
-      </c>
-      <c r="T522">
-        <v>1</v>
-      </c>
-      <c r="U522">
-        <v>1</v>
-      </c>
-      <c r="V522">
-        <v>1</v>
-      </c>
-      <c r="W522">
-        <v>1</v>
-      </c>
-      <c r="X522">
-        <v>1</v>
-      </c>
-      <c r="Y522">
-        <v>1</v>
-      </c>
-      <c r="Z522">
-        <v>1</v>
-      </c>
-      <c r="AA522">
-        <v>1</v>
-      </c>
-      <c r="AB522">
-        <v>1</v>
-      </c>
-      <c r="AC522">
-        <v>1</v>
-      </c>
-      <c r="AD522">
-        <v>1</v>
-      </c>
-      <c r="AE522">
-        <v>1</v>
-      </c>
-      <c r="AF522">
-        <v>1</v>
-      </c>
-      <c r="AG522">
-        <v>1</v>
-      </c>
-      <c r="AH522">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="523" spans="1:34">
-      <c r="A523">
-        <v>1</v>
-      </c>
-      <c r="B523" t="s">
-        <v>755</v>
-      </c>
-      <c r="C523" t="s">
-        <v>930</v>
-      </c>
-      <c r="D523" t="s">
-        <v>952</v>
-      </c>
-      <c r="E523" t="s">
-        <v>992</v>
-      </c>
-      <c r="F523" t="s">
-        <v>590</v>
-      </c>
-      <c r="G523">
-        <v>1</v>
-      </c>
-      <c r="H523">
-        <v>1</v>
-      </c>
-      <c r="I523">
-        <v>1</v>
-      </c>
-      <c r="J523">
-        <v>1</v>
-      </c>
-      <c r="K523">
-        <v>1</v>
-      </c>
-      <c r="L523">
-        <v>1</v>
-      </c>
-      <c r="M523">
-        <v>1</v>
-      </c>
-      <c r="N523">
-        <v>1</v>
-      </c>
-      <c r="O523">
-        <v>1</v>
-      </c>
-      <c r="P523">
-        <v>1</v>
-      </c>
-      <c r="Q523">
-        <v>1</v>
-      </c>
-      <c r="R523">
-        <v>1</v>
-      </c>
-      <c r="S523">
-        <v>1</v>
-      </c>
-      <c r="T523">
-        <v>1</v>
-      </c>
-      <c r="U523">
-        <v>1</v>
-      </c>
-      <c r="V523">
-        <v>1</v>
-      </c>
-      <c r="W523">
-        <v>1</v>
-      </c>
-      <c r="X523">
-        <v>1</v>
-      </c>
-      <c r="Y523">
-        <v>1</v>
-      </c>
-      <c r="Z523">
-        <v>1</v>
-      </c>
-      <c r="AA523">
-        <v>1</v>
-      </c>
-      <c r="AB523">
-        <v>1</v>
-      </c>
-      <c r="AC523">
-        <v>1</v>
-      </c>
-      <c r="AD523">
-        <v>1</v>
-      </c>
-      <c r="AE523">
-        <v>1</v>
-      </c>
-      <c r="AF523">
-        <v>1</v>
-      </c>
-      <c r="AG523">
-        <v>1</v>
-      </c>
-      <c r="AH523">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="524" spans="1:34">
-      <c r="A524">
-        <v>1</v>
-      </c>
-      <c r="B524" t="s">
-        <v>756</v>
-      </c>
-      <c r="C524" t="s">
-        <v>931</v>
-      </c>
-      <c r="D524" t="s">
-        <v>394</v>
-      </c>
-      <c r="E524" t="s">
-        <v>533</v>
-      </c>
-      <c r="F524" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G524">
-        <v>1</v>
-      </c>
-      <c r="H524">
-        <v>1</v>
-      </c>
-      <c r="I524">
-        <v>1</v>
-      </c>
-      <c r="J524">
-        <v>1</v>
-      </c>
-      <c r="K524">
-        <v>1</v>
-      </c>
-      <c r="L524">
-        <v>1</v>
-      </c>
-      <c r="M524">
-        <v>1</v>
-      </c>
-      <c r="N524">
-        <v>1</v>
-      </c>
-      <c r="O524">
-        <v>1</v>
-      </c>
-      <c r="P524">
-        <v>1</v>
-      </c>
-      <c r="Q524">
-        <v>1</v>
-      </c>
-      <c r="R524">
-        <v>1</v>
-      </c>
-      <c r="S524">
-        <v>1</v>
-      </c>
-      <c r="T524">
-        <v>1</v>
-      </c>
-      <c r="U524">
-        <v>1</v>
-      </c>
-      <c r="V524">
-        <v>1</v>
-      </c>
-      <c r="W524">
-        <v>1</v>
-      </c>
-      <c r="X524">
-        <v>1</v>
-      </c>
-      <c r="Y524">
-        <v>1</v>
-      </c>
-      <c r="Z524">
-        <v>1</v>
-      </c>
-      <c r="AA524">
-        <v>1</v>
-      </c>
-      <c r="AB524">
-        <v>1</v>
-      </c>
-      <c r="AC524">
-        <v>1</v>
-      </c>
-      <c r="AD524">
-        <v>1</v>
-      </c>
-      <c r="AE524">
-        <v>1</v>
-      </c>
-      <c r="AF524">
-        <v>1</v>
-      </c>
-      <c r="AG524">
-        <v>1</v>
-      </c>
-      <c r="AH524">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="525" spans="1:34">
-      <c r="A525">
-        <v>1</v>
-      </c>
-      <c r="B525" t="s">
-        <v>756</v>
-      </c>
-      <c r="C525" t="s">
-        <v>931</v>
-      </c>
-      <c r="D525" t="s">
-        <v>953</v>
-      </c>
-      <c r="E525" t="s">
-        <v>993</v>
-      </c>
-      <c r="F525" t="s">
-        <v>590</v>
-      </c>
-      <c r="G525">
-        <v>1</v>
-      </c>
-      <c r="H525">
-        <v>1</v>
-      </c>
-      <c r="I525">
-        <v>1</v>
-      </c>
-      <c r="J525">
-        <v>1</v>
-      </c>
-      <c r="K525">
-        <v>1</v>
-      </c>
-      <c r="L525">
-        <v>1</v>
-      </c>
-      <c r="M525">
-        <v>1</v>
-      </c>
-      <c r="N525">
-        <v>1</v>
-      </c>
-      <c r="O525">
-        <v>1</v>
-      </c>
-      <c r="P525">
-        <v>1</v>
-      </c>
-      <c r="Q525">
-        <v>1</v>
-      </c>
-      <c r="R525">
-        <v>1</v>
-      </c>
-      <c r="S525">
-        <v>1</v>
-      </c>
-      <c r="T525">
-        <v>1</v>
-      </c>
-      <c r="U525">
-        <v>1</v>
-      </c>
-      <c r="V525">
-        <v>1</v>
-      </c>
-      <c r="W525">
-        <v>1</v>
-      </c>
-      <c r="X525">
-        <v>1</v>
-      </c>
-      <c r="Y525">
-        <v>1</v>
-      </c>
-      <c r="Z525">
-        <v>1</v>
-      </c>
-      <c r="AA525">
-        <v>1</v>
-      </c>
-      <c r="AB525">
-        <v>1</v>
-      </c>
-      <c r="AC525">
-        <v>1</v>
-      </c>
-      <c r="AD525">
-        <v>1</v>
-      </c>
-      <c r="AE525">
-        <v>1</v>
-      </c>
-      <c r="AF525">
-        <v>1</v>
-      </c>
-      <c r="AG525">
-        <v>1</v>
-      </c>
-      <c r="AH525">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="526" spans="1:34">
-      <c r="A526">
-        <v>1</v>
-      </c>
-      <c r="B526" t="s">
-        <v>757</v>
-      </c>
-      <c r="C526" t="s">
-        <v>932</v>
-      </c>
-      <c r="D526" t="s">
-        <v>395</v>
-      </c>
-      <c r="E526" t="s">
-        <v>534</v>
-      </c>
-      <c r="F526" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G526">
-        <v>1</v>
-      </c>
-      <c r="H526">
-        <v>1</v>
-      </c>
-      <c r="I526">
-        <v>1</v>
-      </c>
-      <c r="J526">
-        <v>1</v>
-      </c>
-      <c r="K526">
-        <v>1</v>
-      </c>
-      <c r="L526">
-        <v>1</v>
-      </c>
-      <c r="M526">
-        <v>1</v>
-      </c>
-      <c r="N526">
-        <v>1</v>
-      </c>
-      <c r="O526">
-        <v>1</v>
-      </c>
-      <c r="P526">
-        <v>1</v>
-      </c>
-      <c r="Q526">
-        <v>1</v>
-      </c>
-      <c r="R526">
-        <v>1</v>
-      </c>
-      <c r="S526">
-        <v>1</v>
-      </c>
-      <c r="T526">
-        <v>1</v>
-      </c>
-      <c r="U526">
-        <v>1</v>
-      </c>
-      <c r="V526">
-        <v>1</v>
-      </c>
-      <c r="W526">
-        <v>1</v>
-      </c>
-      <c r="X526">
-        <v>1</v>
-      </c>
-      <c r="Y526">
-        <v>1</v>
-      </c>
-      <c r="Z526">
-        <v>1</v>
-      </c>
-      <c r="AA526">
-        <v>1</v>
-      </c>
-      <c r="AB526">
-        <v>1</v>
-      </c>
-      <c r="AC526">
-        <v>1</v>
-      </c>
-      <c r="AD526">
-        <v>1</v>
-      </c>
-      <c r="AE526">
-        <v>1</v>
-      </c>
-      <c r="AF526">
-        <v>1</v>
-      </c>
-      <c r="AG526">
-        <v>1</v>
-      </c>
-      <c r="AH526">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="527" spans="1:34">
-      <c r="A527">
-        <v>1</v>
-      </c>
-      <c r="B527" t="s">
-        <v>757</v>
-      </c>
-      <c r="C527" t="s">
-        <v>932</v>
-      </c>
-      <c r="D527" t="s">
-        <v>954</v>
-      </c>
-      <c r="E527" t="s">
-        <v>994</v>
-      </c>
-      <c r="F527" t="s">
-        <v>590</v>
-      </c>
-      <c r="G527">
-        <v>1</v>
-      </c>
-      <c r="H527">
-        <v>1</v>
-      </c>
-      <c r="I527">
-        <v>1</v>
-      </c>
-      <c r="J527">
-        <v>1</v>
-      </c>
-      <c r="K527">
-        <v>1</v>
-      </c>
-      <c r="L527">
-        <v>1</v>
-      </c>
-      <c r="M527">
-        <v>1</v>
-      </c>
-      <c r="N527">
-        <v>1</v>
-      </c>
-      <c r="O527">
-        <v>1</v>
-      </c>
-      <c r="P527">
-        <v>1</v>
-      </c>
-      <c r="Q527">
-        <v>1</v>
-      </c>
-      <c r="R527">
-        <v>1</v>
-      </c>
-      <c r="S527">
-        <v>1</v>
-      </c>
-      <c r="T527">
-        <v>1</v>
-      </c>
-      <c r="U527">
-        <v>1</v>
-      </c>
-      <c r="V527">
-        <v>1</v>
-      </c>
-      <c r="W527">
-        <v>1</v>
-      </c>
-      <c r="X527">
-        <v>1</v>
-      </c>
-      <c r="Y527">
-        <v>1</v>
-      </c>
-      <c r="Z527">
-        <v>1</v>
-      </c>
-      <c r="AA527">
-        <v>1</v>
-      </c>
-      <c r="AB527">
-        <v>1</v>
-      </c>
-      <c r="AC527">
-        <v>1</v>
-      </c>
-      <c r="AD527">
-        <v>1</v>
-      </c>
-      <c r="AE527">
-        <v>1</v>
-      </c>
-      <c r="AF527">
-        <v>1</v>
-      </c>
-      <c r="AG527">
-        <v>1</v>
-      </c>
-      <c r="AH527">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="528" spans="1:34">
-      <c r="A528">
-        <v>1</v>
-      </c>
-      <c r="B528" t="s">
-        <v>758</v>
-      </c>
-      <c r="C528" t="s">
-        <v>933</v>
-      </c>
-      <c r="D528" t="s">
-        <v>396</v>
-      </c>
-      <c r="E528" t="s">
-        <v>535</v>
-      </c>
-      <c r="F528" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G528">
-        <v>1</v>
-      </c>
-      <c r="H528">
-        <v>1</v>
-      </c>
-      <c r="I528">
-        <v>1</v>
-      </c>
-      <c r="J528">
-        <v>1</v>
-      </c>
-      <c r="K528">
-        <v>1</v>
-      </c>
-      <c r="L528">
-        <v>1</v>
-      </c>
-      <c r="M528">
-        <v>1</v>
-      </c>
-      <c r="N528">
-        <v>1</v>
-      </c>
-      <c r="O528">
-        <v>1</v>
-      </c>
-      <c r="P528">
-        <v>1</v>
-      </c>
-      <c r="Q528">
-        <v>1</v>
-      </c>
-      <c r="R528">
-        <v>1</v>
-      </c>
-      <c r="S528">
-        <v>1</v>
-      </c>
-      <c r="T528">
-        <v>1</v>
-      </c>
-      <c r="U528">
-        <v>1</v>
-      </c>
-      <c r="V528">
-        <v>1</v>
-      </c>
-      <c r="W528">
-        <v>1</v>
-      </c>
-      <c r="X528">
-        <v>1</v>
-      </c>
-      <c r="Y528">
-        <v>1</v>
-      </c>
-      <c r="Z528">
-        <v>1</v>
-      </c>
-      <c r="AA528">
-        <v>1</v>
-      </c>
-      <c r="AB528">
-        <v>1</v>
-      </c>
-      <c r="AC528">
-        <v>1</v>
-      </c>
-      <c r="AD528">
-        <v>1</v>
-      </c>
-      <c r="AE528">
-        <v>1</v>
-      </c>
-      <c r="AF528">
-        <v>1</v>
-      </c>
-      <c r="AG528">
-        <v>1</v>
-      </c>
-      <c r="AH528">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="529" spans="1:34">
-      <c r="A529">
-        <v>1</v>
-      </c>
-      <c r="B529" t="s">
-        <v>758</v>
-      </c>
-      <c r="C529" t="s">
-        <v>933</v>
-      </c>
-      <c r="D529" t="s">
-        <v>955</v>
-      </c>
-      <c r="E529" t="s">
-        <v>995</v>
-      </c>
-      <c r="F529" t="s">
-        <v>590</v>
-      </c>
-      <c r="G529">
-        <v>1</v>
-      </c>
-      <c r="H529">
-        <v>1</v>
-      </c>
-      <c r="I529">
-        <v>1</v>
-      </c>
-      <c r="J529">
-        <v>1</v>
-      </c>
-      <c r="K529">
-        <v>1</v>
-      </c>
-      <c r="L529">
-        <v>1</v>
-      </c>
-      <c r="M529">
-        <v>1</v>
-      </c>
-      <c r="N529">
-        <v>1</v>
-      </c>
-      <c r="O529">
-        <v>1</v>
-      </c>
-      <c r="P529">
-        <v>1</v>
-      </c>
-      <c r="Q529">
-        <v>1</v>
-      </c>
-      <c r="R529">
-        <v>1</v>
-      </c>
-      <c r="S529">
-        <v>1</v>
-      </c>
-      <c r="T529">
-        <v>1</v>
-      </c>
-      <c r="U529">
-        <v>1</v>
-      </c>
-      <c r="V529">
-        <v>1</v>
-      </c>
-      <c r="W529">
-        <v>1</v>
-      </c>
-      <c r="X529">
-        <v>1</v>
-      </c>
-      <c r="Y529">
-        <v>1</v>
-      </c>
-      <c r="Z529">
-        <v>1</v>
-      </c>
-      <c r="AA529">
-        <v>1</v>
-      </c>
-      <c r="AB529">
-        <v>1</v>
-      </c>
-      <c r="AC529">
-        <v>1</v>
-      </c>
-      <c r="AD529">
-        <v>1</v>
-      </c>
-      <c r="AE529">
-        <v>1</v>
-      </c>
-      <c r="AF529">
-        <v>1</v>
-      </c>
-      <c r="AG529">
-        <v>1</v>
-      </c>
-      <c r="AH529">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="530" spans="1:34">
-      <c r="A530">
-        <v>1</v>
-      </c>
-      <c r="B530" t="s">
-        <v>759</v>
-      </c>
-      <c r="C530" t="s">
-        <v>934</v>
-      </c>
-      <c r="D530" t="s">
-        <v>397</v>
-      </c>
-      <c r="E530" t="s">
-        <v>536</v>
-      </c>
-      <c r="F530" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G530">
-        <v>1</v>
-      </c>
-      <c r="H530">
-        <v>1</v>
-      </c>
-      <c r="I530">
-        <v>1</v>
-      </c>
-      <c r="J530">
-        <v>1</v>
-      </c>
-      <c r="K530">
-        <v>1</v>
-      </c>
-      <c r="L530">
-        <v>1</v>
-      </c>
-      <c r="M530">
-        <v>1</v>
-      </c>
-      <c r="N530">
-        <v>1</v>
-      </c>
-      <c r="O530">
-        <v>1</v>
-      </c>
-      <c r="P530">
-        <v>1</v>
-      </c>
-      <c r="Q530">
-        <v>1</v>
-      </c>
-      <c r="R530">
-        <v>1</v>
-      </c>
-      <c r="S530">
-        <v>1</v>
-      </c>
-      <c r="T530">
-        <v>1</v>
-      </c>
-      <c r="U530">
-        <v>1</v>
-      </c>
-      <c r="V530">
-        <v>1</v>
-      </c>
-      <c r="W530">
-        <v>1</v>
-      </c>
-      <c r="X530">
-        <v>1</v>
-      </c>
-      <c r="Y530">
-        <v>1</v>
-      </c>
-      <c r="Z530">
-        <v>1</v>
-      </c>
-      <c r="AA530">
-        <v>1</v>
-      </c>
-      <c r="AB530">
-        <v>1</v>
-      </c>
-      <c r="AC530">
-        <v>1</v>
-      </c>
-      <c r="AD530">
-        <v>1</v>
-      </c>
-      <c r="AE530">
-        <v>1</v>
-      </c>
-      <c r="AF530">
-        <v>1</v>
-      </c>
-      <c r="AG530">
-        <v>1</v>
-      </c>
-      <c r="AH530">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="531" spans="1:34">
-      <c r="A531">
-        <v>1</v>
-      </c>
-      <c r="B531" t="s">
-        <v>759</v>
-      </c>
-      <c r="C531" t="s">
-        <v>934</v>
-      </c>
-      <c r="D531" t="s">
-        <v>956</v>
-      </c>
-      <c r="E531" t="s">
-        <v>996</v>
-      </c>
-      <c r="F531" t="s">
-        <v>590</v>
-      </c>
-      <c r="G531">
-        <v>1</v>
-      </c>
-      <c r="H531">
-        <v>1</v>
-      </c>
-      <c r="I531">
-        <v>1</v>
-      </c>
-      <c r="J531">
-        <v>1</v>
-      </c>
-      <c r="K531">
-        <v>1</v>
-      </c>
-      <c r="L531">
-        <v>1</v>
-      </c>
-      <c r="M531">
-        <v>1</v>
-      </c>
-      <c r="N531">
-        <v>1</v>
-      </c>
-      <c r="O531">
-        <v>1</v>
-      </c>
-      <c r="P531">
-        <v>1</v>
-      </c>
-      <c r="Q531">
-        <v>1</v>
-      </c>
-      <c r="R531">
-        <v>1</v>
-      </c>
-      <c r="S531">
-        <v>1</v>
-      </c>
-      <c r="T531">
-        <v>1</v>
-      </c>
-      <c r="U531">
-        <v>1</v>
-      </c>
-      <c r="V531">
-        <v>1</v>
-      </c>
-      <c r="W531">
-        <v>1</v>
-      </c>
-      <c r="X531">
-        <v>1</v>
-      </c>
-      <c r="Y531">
-        <v>1</v>
-      </c>
-      <c r="Z531">
-        <v>1</v>
-      </c>
-      <c r="AA531">
-        <v>1</v>
-      </c>
-      <c r="AB531">
-        <v>1</v>
-      </c>
-      <c r="AC531">
-        <v>1</v>
-      </c>
-      <c r="AD531">
-        <v>1</v>
-      </c>
-      <c r="AE531">
-        <v>1</v>
-      </c>
-      <c r="AF531">
-        <v>1</v>
-      </c>
-      <c r="AG531">
-        <v>1</v>
-      </c>
-      <c r="AH531">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="532" spans="1:34">
-      <c r="A532">
-        <v>1</v>
-      </c>
-      <c r="B532" t="s">
-        <v>760</v>
-      </c>
-      <c r="C532" t="s">
-        <v>935</v>
-      </c>
-      <c r="D532" t="s">
-        <v>439</v>
-      </c>
-      <c r="E532" t="s">
-        <v>578</v>
-      </c>
-      <c r="F532" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G532">
-        <v>1</v>
-      </c>
-      <c r="H532">
-        <v>1</v>
-      </c>
-      <c r="I532">
-        <v>1</v>
-      </c>
-      <c r="J532">
-        <v>1</v>
-      </c>
-      <c r="K532">
-        <v>1</v>
-      </c>
-      <c r="L532">
-        <v>1</v>
-      </c>
-      <c r="M532">
-        <v>1</v>
-      </c>
-      <c r="N532">
-        <v>1</v>
-      </c>
-      <c r="O532">
-        <v>1</v>
-      </c>
-      <c r="P532">
-        <v>1</v>
-      </c>
-      <c r="Q532">
-        <v>1</v>
-      </c>
-      <c r="R532">
-        <v>1</v>
-      </c>
-      <c r="S532">
-        <v>1</v>
-      </c>
-      <c r="T532">
-        <v>1</v>
-      </c>
-      <c r="U532">
-        <v>1</v>
-      </c>
-      <c r="V532">
-        <v>1</v>
-      </c>
-      <c r="W532">
-        <v>1</v>
-      </c>
-      <c r="X532">
-        <v>1</v>
-      </c>
-      <c r="Y532">
-        <v>1</v>
-      </c>
-      <c r="Z532">
-        <v>1</v>
-      </c>
-      <c r="AA532">
-        <v>1</v>
-      </c>
-      <c r="AB532">
-        <v>1</v>
-      </c>
-      <c r="AC532">
-        <v>1</v>
-      </c>
-      <c r="AD532">
-        <v>1</v>
-      </c>
-      <c r="AE532">
-        <v>1</v>
-      </c>
-      <c r="AF532">
-        <v>1</v>
-      </c>
-      <c r="AG532">
-        <v>1</v>
-      </c>
-      <c r="AH532">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="533" spans="1:34">
-      <c r="A533">
-        <v>1</v>
-      </c>
-      <c r="B533" t="s">
-        <v>760</v>
-      </c>
-      <c r="C533" t="s">
-        <v>935</v>
-      </c>
-      <c r="D533" t="s">
-        <v>960</v>
-      </c>
-      <c r="E533" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F533" t="s">
-        <v>590</v>
-      </c>
-      <c r="G533">
-        <v>1</v>
-      </c>
-      <c r="H533">
-        <v>1</v>
-      </c>
-      <c r="I533">
-        <v>1</v>
-      </c>
-      <c r="J533">
-        <v>1</v>
-      </c>
-      <c r="K533">
-        <v>1</v>
-      </c>
-      <c r="L533">
-        <v>1</v>
-      </c>
-      <c r="M533">
-        <v>1</v>
-      </c>
-      <c r="N533">
-        <v>1</v>
-      </c>
-      <c r="O533">
-        <v>1</v>
-      </c>
-      <c r="P533">
-        <v>1</v>
-      </c>
-      <c r="Q533">
-        <v>1</v>
-      </c>
-      <c r="R533">
-        <v>1</v>
-      </c>
-      <c r="S533">
-        <v>1</v>
-      </c>
-      <c r="T533">
-        <v>1</v>
-      </c>
-      <c r="U533">
-        <v>1</v>
-      </c>
-      <c r="V533">
-        <v>1</v>
-      </c>
-      <c r="W533">
-        <v>1</v>
-      </c>
-      <c r="X533">
-        <v>1</v>
-      </c>
-      <c r="Y533">
-        <v>1</v>
-      </c>
-      <c r="Z533">
-        <v>1</v>
-      </c>
-      <c r="AA533">
-        <v>1</v>
-      </c>
-      <c r="AB533">
-        <v>1</v>
-      </c>
-      <c r="AC533">
-        <v>1</v>
-      </c>
-      <c r="AD533">
-        <v>1</v>
-      </c>
-      <c r="AE533">
-        <v>1</v>
-      </c>
-      <c r="AF533">
-        <v>1</v>
-      </c>
-      <c r="AG533">
-        <v>1</v>
-      </c>
-      <c r="AH533">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="534" spans="1:34">
-      <c r="A534">
-        <v>1</v>
-      </c>
-      <c r="B534" t="s">
-        <v>761</v>
-      </c>
-      <c r="C534" t="s">
-        <v>936</v>
-      </c>
-      <c r="D534" t="s">
-        <v>449</v>
-      </c>
-      <c r="E534" t="s">
-        <v>588</v>
-      </c>
-      <c r="F534" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G534">
-        <v>1</v>
-      </c>
-      <c r="H534">
-        <v>1</v>
-      </c>
-      <c r="I534">
-        <v>1</v>
-      </c>
-      <c r="J534">
-        <v>1</v>
-      </c>
-      <c r="K534">
-        <v>1</v>
-      </c>
-      <c r="L534">
-        <v>1</v>
-      </c>
-      <c r="M534">
-        <v>1</v>
-      </c>
-      <c r="N534">
-        <v>1</v>
-      </c>
-      <c r="O534">
-        <v>1</v>
-      </c>
-      <c r="P534">
-        <v>1</v>
-      </c>
-      <c r="Q534">
-        <v>1</v>
-      </c>
-      <c r="R534">
-        <v>1</v>
-      </c>
-      <c r="S534">
-        <v>1</v>
-      </c>
-      <c r="T534">
-        <v>1</v>
-      </c>
-      <c r="U534">
-        <v>1</v>
-      </c>
-      <c r="V534">
-        <v>1</v>
-      </c>
-      <c r="W534">
-        <v>1</v>
-      </c>
-      <c r="X534">
-        <v>1</v>
-      </c>
-      <c r="Y534">
-        <v>1</v>
-      </c>
-      <c r="Z534">
-        <v>1</v>
-      </c>
-      <c r="AA534">
-        <v>1</v>
-      </c>
-      <c r="AB534">
-        <v>1</v>
-      </c>
-      <c r="AC534">
-        <v>1</v>
-      </c>
-      <c r="AD534">
-        <v>1</v>
-      </c>
-      <c r="AE534">
-        <v>1</v>
-      </c>
-      <c r="AF534">
-        <v>1</v>
-      </c>
-      <c r="AG534">
-        <v>1</v>
-      </c>
-      <c r="AH534">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="535" spans="1:34">
-      <c r="A535">
-        <v>1</v>
-      </c>
-      <c r="B535" t="s">
-        <v>761</v>
-      </c>
-      <c r="C535" t="s">
-        <v>936</v>
-      </c>
-      <c r="D535" t="s">
-        <v>960</v>
-      </c>
-      <c r="E535" t="s">
-        <v>1024</v>
-      </c>
-      <c r="F535" t="s">
-        <v>590</v>
-      </c>
-      <c r="G535">
-        <v>1</v>
-      </c>
-      <c r="H535">
-        <v>1</v>
-      </c>
-      <c r="I535">
-        <v>1</v>
-      </c>
-      <c r="J535">
-        <v>1</v>
-      </c>
-      <c r="K535">
-        <v>1</v>
-      </c>
-      <c r="L535">
-        <v>1</v>
-      </c>
-      <c r="M535">
-        <v>1</v>
-      </c>
-      <c r="N535">
-        <v>1</v>
-      </c>
-      <c r="O535">
-        <v>1</v>
-      </c>
-      <c r="P535">
-        <v>1</v>
-      </c>
-      <c r="Q535">
-        <v>1</v>
-      </c>
-      <c r="R535">
-        <v>1</v>
-      </c>
-      <c r="S535">
-        <v>1</v>
-      </c>
-      <c r="T535">
-        <v>1</v>
-      </c>
-      <c r="U535">
-        <v>1</v>
-      </c>
-      <c r="V535">
-        <v>1</v>
-      </c>
-      <c r="W535">
-        <v>1</v>
-      </c>
-      <c r="X535">
-        <v>1</v>
-      </c>
-      <c r="Y535">
-        <v>1</v>
-      </c>
-      <c r="Z535">
-        <v>1</v>
-      </c>
-      <c r="AA535">
-        <v>1</v>
-      </c>
-      <c r="AB535">
-        <v>1</v>
-      </c>
-      <c r="AC535">
-        <v>1</v>
-      </c>
-      <c r="AD535">
-        <v>1</v>
-      </c>
-      <c r="AE535">
-        <v>1</v>
-      </c>
-      <c r="AF535">
-        <v>1</v>
-      </c>
-      <c r="AG535">
-        <v>1</v>
-      </c>
-      <c r="AH535">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="536" spans="1:34">
-      <c r="A536">
-        <v>1</v>
-      </c>
-      <c r="B536" t="s">
-        <v>762</v>
-      </c>
-      <c r="C536" t="s">
-        <v>937</v>
-      </c>
-      <c r="D536" t="s">
-        <v>967</v>
-      </c>
-      <c r="E536" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F536" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G536">
-        <v>1</v>
-      </c>
-      <c r="H536">
-        <v>1</v>
-      </c>
-      <c r="I536">
-        <v>1</v>
-      </c>
-      <c r="J536">
-        <v>1</v>
-      </c>
-      <c r="K536">
-        <v>1</v>
-      </c>
-      <c r="L536">
-        <v>1</v>
-      </c>
-      <c r="M536">
-        <v>1</v>
-      </c>
-      <c r="N536">
-        <v>1</v>
-      </c>
-      <c r="O536">
-        <v>1</v>
-      </c>
-      <c r="P536">
-        <v>1</v>
-      </c>
-      <c r="Q536">
-        <v>1</v>
-      </c>
-      <c r="R536">
-        <v>1</v>
-      </c>
-      <c r="S536">
-        <v>1</v>
-      </c>
-      <c r="T536">
-        <v>1</v>
-      </c>
-      <c r="U536">
-        <v>1</v>
-      </c>
-      <c r="V536">
-        <v>1</v>
-      </c>
-      <c r="W536">
-        <v>1</v>
-      </c>
-      <c r="X536">
-        <v>1</v>
-      </c>
-      <c r="Y536">
-        <v>1</v>
-      </c>
-      <c r="Z536">
-        <v>1</v>
-      </c>
-      <c r="AA536">
-        <v>1</v>
-      </c>
-      <c r="AB536">
-        <v>1</v>
-      </c>
-      <c r="AC536">
-        <v>1</v>
-      </c>
-      <c r="AD536">
-        <v>1</v>
-      </c>
-      <c r="AE536">
-        <v>1</v>
-      </c>
-      <c r="AF536">
-        <v>1</v>
-      </c>
-      <c r="AG536">
-        <v>1</v>
-      </c>
-      <c r="AH536">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="537" spans="1:34">
-      <c r="A537">
-        <v>2</v>
-      </c>
-      <c r="B537" t="s">
-        <v>762</v>
-      </c>
-      <c r="C537" t="s">
-        <v>937</v>
-      </c>
-      <c r="D537" t="s">
-        <v>961</v>
-      </c>
-      <c r="E537" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F537" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G537">
-        <v>1</v>
-      </c>
-      <c r="H537">
-        <v>1</v>
-      </c>
-      <c r="I537">
-        <v>1</v>
-      </c>
-      <c r="J537">
-        <v>1</v>
-      </c>
-      <c r="K537">
-        <v>1</v>
-      </c>
-      <c r="L537">
-        <v>1</v>
-      </c>
-      <c r="M537">
-        <v>1</v>
-      </c>
-      <c r="N537">
-        <v>1</v>
-      </c>
-      <c r="O537">
-        <v>1</v>
-      </c>
-      <c r="P537">
-        <v>1</v>
-      </c>
-      <c r="Q537">
-        <v>1</v>
-      </c>
-      <c r="R537">
-        <v>1</v>
-      </c>
-      <c r="S537">
-        <v>1</v>
-      </c>
-      <c r="T537">
-        <v>1</v>
-      </c>
-      <c r="U537">
-        <v>1</v>
-      </c>
-      <c r="V537">
-        <v>1</v>
-      </c>
-      <c r="W537">
-        <v>1</v>
-      </c>
-      <c r="X537">
-        <v>1</v>
-      </c>
-      <c r="Y537">
-        <v>1</v>
-      </c>
-      <c r="Z537">
-        <v>1</v>
-      </c>
-      <c r="AA537">
-        <v>1</v>
-      </c>
-      <c r="AB537">
-        <v>1</v>
-      </c>
-      <c r="AC537">
-        <v>1</v>
-      </c>
-      <c r="AD537">
-        <v>1</v>
-      </c>
-      <c r="AE537">
-        <v>1</v>
-      </c>
-      <c r="AF537">
-        <v>1</v>
-      </c>
-      <c r="AG537">
-        <v>1</v>
-      </c>
-      <c r="AH537">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="538" spans="1:34">
-      <c r="A538">
-        <v>1</v>
-      </c>
-      <c r="B538" t="s">
-        <v>762</v>
-      </c>
-      <c r="C538" t="s">
-        <v>937</v>
-      </c>
-      <c r="D538" t="s">
-        <v>964</v>
-      </c>
-      <c r="E538" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F538" t="s">
-        <v>590</v>
-      </c>
-      <c r="G538">
-        <v>0.95</v>
-      </c>
-      <c r="H538">
-        <v>0.95</v>
-      </c>
-      <c r="I538">
-        <v>0.95</v>
-      </c>
-      <c r="J538">
-        <v>0.95</v>
-      </c>
-      <c r="K538">
-        <v>0.95</v>
-      </c>
-      <c r="L538">
-        <v>0.95</v>
-      </c>
-      <c r="M538">
-        <v>0.95</v>
-      </c>
-      <c r="N538">
-        <v>0.95</v>
-      </c>
-      <c r="O538">
-        <v>0.95</v>
-      </c>
-      <c r="P538">
-        <v>0.95</v>
-      </c>
-      <c r="Q538">
-        <v>0.95</v>
-      </c>
-      <c r="R538">
-        <v>0.95</v>
-      </c>
-      <c r="S538">
-        <v>0.95</v>
-      </c>
-      <c r="T538">
-        <v>0.95</v>
-      </c>
-      <c r="U538">
-        <v>0.95</v>
-      </c>
-      <c r="V538">
-        <v>0.95</v>
-      </c>
-      <c r="W538">
-        <v>0.95</v>
-      </c>
-      <c r="X538">
-        <v>0.95</v>
-      </c>
-      <c r="Y538">
-        <v>0.95</v>
-      </c>
-      <c r="Z538">
-        <v>0.95</v>
-      </c>
-      <c r="AA538">
-        <v>0.95</v>
-      </c>
-      <c r="AB538">
-        <v>0.95</v>
-      </c>
-      <c r="AC538">
-        <v>0.95</v>
-      </c>
-      <c r="AD538">
-        <v>0.95</v>
-      </c>
-      <c r="AE538">
-        <v>0.95</v>
-      </c>
-      <c r="AF538">
-        <v>0.95</v>
-      </c>
-      <c r="AG538">
-        <v>0.95</v>
-      </c>
-      <c r="AH538">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="539" spans="1:34">
-      <c r="A539">
-        <v>2</v>
-      </c>
-      <c r="B539" t="s">
-        <v>762</v>
-      </c>
-      <c r="C539" t="s">
-        <v>937</v>
-      </c>
-      <c r="D539" t="s">
-        <v>968</v>
-      </c>
-      <c r="E539" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F539" t="s">
-        <v>590</v>
-      </c>
-      <c r="G539">
-        <v>0.95</v>
-      </c>
-      <c r="H539">
-        <v>0.95</v>
-      </c>
-      <c r="I539">
-        <v>0.95</v>
-      </c>
-      <c r="J539">
-        <v>0.95</v>
-      </c>
-      <c r="K539">
-        <v>0.95</v>
-      </c>
-      <c r="L539">
-        <v>0.95</v>
-      </c>
-      <c r="M539">
-        <v>0.95</v>
-      </c>
-      <c r="N539">
-        <v>0.95</v>
-      </c>
-      <c r="O539">
-        <v>0.95</v>
-      </c>
-      <c r="P539">
-        <v>0.95</v>
-      </c>
-      <c r="Q539">
-        <v>0.95</v>
-      </c>
-      <c r="R539">
-        <v>0.95</v>
-      </c>
-      <c r="S539">
-        <v>0.95</v>
-      </c>
-      <c r="T539">
-        <v>0.95</v>
-      </c>
-      <c r="U539">
-        <v>0.95</v>
-      </c>
-      <c r="V539">
-        <v>0.95</v>
-      </c>
-      <c r="W539">
-        <v>0.95</v>
-      </c>
-      <c r="X539">
-        <v>0.95</v>
-      </c>
-      <c r="Y539">
-        <v>0.95</v>
-      </c>
-      <c r="Z539">
-        <v>0.95</v>
-      </c>
-      <c r="AA539">
-        <v>0.95</v>
-      </c>
-      <c r="AB539">
-        <v>0.95</v>
-      </c>
-      <c r="AC539">
-        <v>0.95</v>
-      </c>
-      <c r="AD539">
-        <v>0.95</v>
-      </c>
-      <c r="AE539">
-        <v>0.95</v>
-      </c>
-      <c r="AF539">
-        <v>0.95</v>
-      </c>
-      <c r="AG539">
-        <v>0.95</v>
-      </c>
-      <c r="AH539">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="540" spans="1:34">
-      <c r="A540">
-        <v>1</v>
-      </c>
-      <c r="B540" t="s">
-        <v>763</v>
-      </c>
-      <c r="C540" t="s">
-        <v>938</v>
-      </c>
-      <c r="D540" t="s">
-        <v>967</v>
-      </c>
-      <c r="E540" t="s">
-        <v>1007</v>
-      </c>
-      <c r="F540" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G540">
-        <v>1</v>
-      </c>
-      <c r="H540">
-        <v>1</v>
-      </c>
-      <c r="I540">
-        <v>1</v>
-      </c>
-      <c r="J540">
-        <v>1</v>
-      </c>
-      <c r="K540">
-        <v>1</v>
-      </c>
-      <c r="L540">
-        <v>1</v>
-      </c>
-      <c r="M540">
-        <v>1</v>
-      </c>
-      <c r="N540">
-        <v>1</v>
-      </c>
-      <c r="O540">
-        <v>1</v>
-      </c>
-      <c r="P540">
-        <v>1</v>
-      </c>
-      <c r="Q540">
-        <v>1</v>
-      </c>
-      <c r="R540">
-        <v>1</v>
-      </c>
-      <c r="S540">
-        <v>1</v>
-      </c>
-      <c r="T540">
-        <v>1</v>
-      </c>
-      <c r="U540">
-        <v>1</v>
-      </c>
-      <c r="V540">
-        <v>1</v>
-      </c>
-      <c r="W540">
-        <v>1</v>
-      </c>
-      <c r="X540">
-        <v>1</v>
-      </c>
-      <c r="Y540">
-        <v>1</v>
-      </c>
-      <c r="Z540">
-        <v>1</v>
-      </c>
-      <c r="AA540">
-        <v>1</v>
-      </c>
-      <c r="AB540">
-        <v>1</v>
-      </c>
-      <c r="AC540">
-        <v>1</v>
-      </c>
-      <c r="AD540">
-        <v>1</v>
-      </c>
-      <c r="AE540">
-        <v>1</v>
-      </c>
-      <c r="AF540">
-        <v>1</v>
-      </c>
-      <c r="AG540">
-        <v>1</v>
-      </c>
-      <c r="AH540">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="541" spans="1:34">
-      <c r="A541">
-        <v>2</v>
-      </c>
-      <c r="B541" t="s">
-        <v>763</v>
-      </c>
-      <c r="C541" t="s">
-        <v>938</v>
-      </c>
-      <c r="D541" t="s">
-        <v>965</v>
-      </c>
-      <c r="E541" t="s">
-        <v>1005</v>
-      </c>
-      <c r="F541" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G541">
-        <v>1</v>
-      </c>
-      <c r="H541">
-        <v>1</v>
-      </c>
-      <c r="I541">
-        <v>1</v>
-      </c>
-      <c r="J541">
-        <v>1</v>
-      </c>
-      <c r="K541">
-        <v>1</v>
-      </c>
-      <c r="L541">
-        <v>1</v>
-      </c>
-      <c r="M541">
-        <v>1</v>
-      </c>
-      <c r="N541">
-        <v>1</v>
-      </c>
-      <c r="O541">
-        <v>1</v>
-      </c>
-      <c r="P541">
-        <v>1</v>
-      </c>
-      <c r="Q541">
-        <v>1</v>
-      </c>
-      <c r="R541">
-        <v>1</v>
-      </c>
-      <c r="S541">
-        <v>1</v>
-      </c>
-      <c r="T541">
-        <v>1</v>
-      </c>
-      <c r="U541">
-        <v>1</v>
-      </c>
-      <c r="V541">
-        <v>1</v>
-      </c>
-      <c r="W541">
-        <v>1</v>
-      </c>
-      <c r="X541">
-        <v>1</v>
-      </c>
-      <c r="Y541">
-        <v>1</v>
-      </c>
-      <c r="Z541">
-        <v>1</v>
-      </c>
-      <c r="AA541">
-        <v>1</v>
-      </c>
-      <c r="AB541">
-        <v>1</v>
-      </c>
-      <c r="AC541">
-        <v>1</v>
-      </c>
-      <c r="AD541">
-        <v>1</v>
-      </c>
-      <c r="AE541">
-        <v>1</v>
-      </c>
-      <c r="AF541">
-        <v>1</v>
-      </c>
-      <c r="AG541">
-        <v>1</v>
-      </c>
-      <c r="AH541">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="542" spans="1:34">
-      <c r="A542">
-        <v>1</v>
-      </c>
-      <c r="B542" t="s">
-        <v>763</v>
-      </c>
-      <c r="C542" t="s">
-        <v>938</v>
-      </c>
-      <c r="D542" t="s">
-        <v>966</v>
-      </c>
-      <c r="E542" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F542" t="s">
-        <v>590</v>
-      </c>
-      <c r="G542">
-        <v>0.95</v>
-      </c>
-      <c r="H542">
-        <v>0.95</v>
-      </c>
-      <c r="I542">
-        <v>0.95</v>
-      </c>
-      <c r="J542">
-        <v>0.95</v>
-      </c>
-      <c r="K542">
-        <v>0.95</v>
-      </c>
-      <c r="L542">
-        <v>0.95</v>
-      </c>
-      <c r="M542">
-        <v>0.95</v>
-      </c>
-      <c r="N542">
-        <v>0.95</v>
-      </c>
-      <c r="O542">
-        <v>0.95</v>
-      </c>
-      <c r="P542">
-        <v>0.95</v>
-      </c>
-      <c r="Q542">
-        <v>0.95</v>
-      </c>
-      <c r="R542">
-        <v>0.95</v>
-      </c>
-      <c r="S542">
-        <v>0.95</v>
-      </c>
-      <c r="T542">
-        <v>0.95</v>
-      </c>
-      <c r="U542">
-        <v>0.95</v>
-      </c>
-      <c r="V542">
-        <v>0.95</v>
-      </c>
-      <c r="W542">
-        <v>0.95</v>
-      </c>
-      <c r="X542">
-        <v>0.95</v>
-      </c>
-      <c r="Y542">
-        <v>0.95</v>
-      </c>
-      <c r="Z542">
-        <v>0.95</v>
-      </c>
-      <c r="AA542">
-        <v>0.95</v>
-      </c>
-      <c r="AB542">
-        <v>0.95</v>
-      </c>
-      <c r="AC542">
-        <v>0.95</v>
-      </c>
-      <c r="AD542">
-        <v>0.95</v>
-      </c>
-      <c r="AE542">
-        <v>0.95</v>
-      </c>
-      <c r="AF542">
-        <v>0.95</v>
-      </c>
-      <c r="AG542">
-        <v>0.95</v>
-      </c>
-      <c r="AH542">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="543" spans="1:34">
-      <c r="A543">
-        <v>2</v>
-      </c>
-      <c r="B543" t="s">
-        <v>763</v>
-      </c>
-      <c r="C543" t="s">
-        <v>938</v>
-      </c>
-      <c r="D543" t="s">
-        <v>968</v>
-      </c>
-      <c r="E543" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F543" t="s">
-        <v>590</v>
-      </c>
-      <c r="G543">
-        <v>0.95</v>
-      </c>
-      <c r="H543">
-        <v>0.95</v>
-      </c>
-      <c r="I543">
-        <v>0.95</v>
-      </c>
-      <c r="J543">
-        <v>0.95</v>
-      </c>
-      <c r="K543">
-        <v>0.95</v>
-      </c>
-      <c r="L543">
-        <v>0.95</v>
-      </c>
-      <c r="M543">
-        <v>0.95</v>
-      </c>
-      <c r="N543">
-        <v>0.95</v>
-      </c>
-      <c r="O543">
-        <v>0.95</v>
-      </c>
-      <c r="P543">
-        <v>0.95</v>
-      </c>
-      <c r="Q543">
-        <v>0.95</v>
-      </c>
-      <c r="R543">
-        <v>0.95</v>
-      </c>
-      <c r="S543">
-        <v>0.95</v>
-      </c>
-      <c r="T543">
-        <v>0.95</v>
-      </c>
-      <c r="U543">
-        <v>0.95</v>
-      </c>
-      <c r="V543">
-        <v>0.95</v>
-      </c>
-      <c r="W543">
-        <v>0.95</v>
-      </c>
-      <c r="X543">
-        <v>0.95</v>
-      </c>
-      <c r="Y543">
-        <v>0.95</v>
-      </c>
-      <c r="Z543">
-        <v>0.95</v>
-      </c>
-      <c r="AA543">
-        <v>0.95</v>
-      </c>
-      <c r="AB543">
-        <v>0.95</v>
-      </c>
-      <c r="AC543">
-        <v>0.95</v>
-      </c>
-      <c r="AD543">
-        <v>0.95</v>
-      </c>
-      <c r="AE543">
-        <v>0.95</v>
-      </c>
-      <c r="AF543">
-        <v>0.95</v>
-      </c>
-      <c r="AG543">
-        <v>0.95</v>
-      </c>
-      <c r="AH543">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="544" spans="1:34">
-      <c r="A544">
-        <v>1</v>
-      </c>
-      <c r="B544" t="s">
-        <v>764</v>
-      </c>
-      <c r="C544" t="s">
-        <v>939</v>
-      </c>
-      <c r="D544" t="s">
-        <v>979</v>
-      </c>
-      <c r="E544" t="s">
-        <v>1019</v>
-      </c>
-      <c r="F544" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G544">
-        <v>1</v>
-      </c>
-      <c r="H544">
-        <v>1</v>
-      </c>
-      <c r="I544">
-        <v>1</v>
-      </c>
-      <c r="J544">
-        <v>1</v>
-      </c>
-      <c r="K544">
-        <v>1</v>
-      </c>
-      <c r="L544">
-        <v>1</v>
-      </c>
-      <c r="M544">
-        <v>1</v>
-      </c>
-      <c r="N544">
-        <v>1</v>
-      </c>
-      <c r="O544">
-        <v>1</v>
-      </c>
-      <c r="P544">
-        <v>1</v>
-      </c>
-      <c r="Q544">
-        <v>1</v>
-      </c>
-      <c r="R544">
-        <v>1</v>
-      </c>
-      <c r="S544">
-        <v>1</v>
-      </c>
-      <c r="T544">
-        <v>1</v>
-      </c>
-      <c r="U544">
-        <v>1</v>
-      </c>
-      <c r="V544">
-        <v>1</v>
-      </c>
-      <c r="W544">
-        <v>1</v>
-      </c>
-      <c r="X544">
-        <v>1</v>
-      </c>
-      <c r="Y544">
-        <v>1</v>
-      </c>
-      <c r="Z544">
-        <v>1</v>
-      </c>
-      <c r="AA544">
-        <v>1</v>
-      </c>
-      <c r="AB544">
-        <v>1</v>
-      </c>
-      <c r="AC544">
-        <v>1</v>
-      </c>
-      <c r="AD544">
-        <v>1</v>
-      </c>
-      <c r="AE544">
-        <v>1</v>
-      </c>
-      <c r="AF544">
-        <v>1</v>
-      </c>
-      <c r="AG544">
-        <v>1</v>
-      </c>
-      <c r="AH544">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="545" spans="1:34">
-      <c r="A545">
-        <v>2</v>
-      </c>
-      <c r="B545" t="s">
-        <v>764</v>
-      </c>
-      <c r="C545" t="s">
-        <v>939</v>
-      </c>
-      <c r="D545" t="s">
-        <v>971</v>
-      </c>
-      <c r="E545" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F545" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G545">
-        <v>1</v>
-      </c>
-      <c r="H545">
-        <v>1</v>
-      </c>
-      <c r="I545">
-        <v>1</v>
-      </c>
-      <c r="J545">
-        <v>1</v>
-      </c>
-      <c r="K545">
-        <v>1</v>
-      </c>
-      <c r="L545">
-        <v>1</v>
-      </c>
-      <c r="M545">
-        <v>1</v>
-      </c>
-      <c r="N545">
-        <v>1</v>
-      </c>
-      <c r="O545">
-        <v>1</v>
-      </c>
-      <c r="P545">
-        <v>1</v>
-      </c>
-      <c r="Q545">
-        <v>1</v>
-      </c>
-      <c r="R545">
-        <v>1</v>
-      </c>
-      <c r="S545">
-        <v>1</v>
-      </c>
-      <c r="T545">
-        <v>1</v>
-      </c>
-      <c r="U545">
-        <v>1</v>
-      </c>
-      <c r="V545">
-        <v>1</v>
-      </c>
-      <c r="W545">
-        <v>1</v>
-      </c>
-      <c r="X545">
-        <v>1</v>
-      </c>
-      <c r="Y545">
-        <v>1</v>
-      </c>
-      <c r="Z545">
-        <v>1</v>
-      </c>
-      <c r="AA545">
-        <v>1</v>
-      </c>
-      <c r="AB545">
-        <v>1</v>
-      </c>
-      <c r="AC545">
-        <v>1</v>
-      </c>
-      <c r="AD545">
-        <v>1</v>
-      </c>
-      <c r="AE545">
-        <v>1</v>
-      </c>
-      <c r="AF545">
-        <v>1</v>
-      </c>
-      <c r="AG545">
-        <v>1</v>
-      </c>
-      <c r="AH545">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="546" spans="1:34">
-      <c r="A546">
-        <v>1</v>
-      </c>
-      <c r="B546" t="s">
-        <v>764</v>
-      </c>
-      <c r="C546" t="s">
-        <v>939</v>
-      </c>
-      <c r="D546" t="s">
-        <v>972</v>
-      </c>
-      <c r="E546" t="s">
-        <v>1012</v>
-      </c>
-      <c r="F546" t="s">
-        <v>590</v>
-      </c>
-      <c r="G546">
-        <v>0.95</v>
-      </c>
-      <c r="H546">
-        <v>0.95</v>
-      </c>
-      <c r="I546">
-        <v>0.95</v>
-      </c>
-      <c r="J546">
-        <v>0.95</v>
-      </c>
-      <c r="K546">
-        <v>0.95</v>
-      </c>
-      <c r="L546">
-        <v>0.95</v>
-      </c>
-      <c r="M546">
-        <v>0.95</v>
-      </c>
-      <c r="N546">
-        <v>0.95</v>
-      </c>
-      <c r="O546">
-        <v>0.95</v>
-      </c>
-      <c r="P546">
-        <v>0.95</v>
-      </c>
-      <c r="Q546">
-        <v>0.95</v>
-      </c>
-      <c r="R546">
-        <v>0.95</v>
-      </c>
-      <c r="S546">
-        <v>0.95</v>
-      </c>
-      <c r="T546">
-        <v>0.95</v>
-      </c>
-      <c r="U546">
-        <v>0.95</v>
-      </c>
-      <c r="V546">
-        <v>0.95</v>
-      </c>
-      <c r="W546">
-        <v>0.95</v>
-      </c>
-      <c r="X546">
-        <v>0.95</v>
-      </c>
-      <c r="Y546">
-        <v>0.95</v>
-      </c>
-      <c r="Z546">
-        <v>0.95</v>
-      </c>
-      <c r="AA546">
-        <v>0.95</v>
-      </c>
-      <c r="AB546">
-        <v>0.95</v>
-      </c>
-      <c r="AC546">
-        <v>0.95</v>
-      </c>
-      <c r="AD546">
-        <v>0.95</v>
-      </c>
-      <c r="AE546">
-        <v>0.95</v>
-      </c>
-      <c r="AF546">
-        <v>0.95</v>
-      </c>
-      <c r="AG546">
-        <v>0.95</v>
-      </c>
-      <c r="AH546">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="547" spans="1:34">
-      <c r="A547">
-        <v>2</v>
-      </c>
-      <c r="B547" t="s">
-        <v>764</v>
-      </c>
-      <c r="C547" t="s">
-        <v>939</v>
-      </c>
-      <c r="D547" t="s">
-        <v>980</v>
-      </c>
-      <c r="E547" t="s">
-        <v>1020</v>
-      </c>
-      <c r="F547" t="s">
-        <v>590</v>
-      </c>
-      <c r="G547">
-        <v>0.95</v>
-      </c>
-      <c r="H547">
-        <v>0.95</v>
-      </c>
-      <c r="I547">
-        <v>0.95</v>
-      </c>
-      <c r="J547">
-        <v>0.95</v>
-      </c>
-      <c r="K547">
-        <v>0.95</v>
-      </c>
-      <c r="L547">
-        <v>0.95</v>
-      </c>
-      <c r="M547">
-        <v>0.95</v>
-      </c>
-      <c r="N547">
-        <v>0.95</v>
-      </c>
-      <c r="O547">
-        <v>0.95</v>
-      </c>
-      <c r="P547">
-        <v>0.95</v>
-      </c>
-      <c r="Q547">
-        <v>0.95</v>
-      </c>
-      <c r="R547">
-        <v>0.95</v>
-      </c>
-      <c r="S547">
-        <v>0.95</v>
-      </c>
-      <c r="T547">
-        <v>0.95</v>
-      </c>
-      <c r="U547">
-        <v>0.95</v>
-      </c>
-      <c r="V547">
-        <v>0.95</v>
-      </c>
-      <c r="W547">
-        <v>0.95</v>
-      </c>
-      <c r="X547">
-        <v>0.95</v>
-      </c>
-      <c r="Y547">
-        <v>0.95</v>
-      </c>
-      <c r="Z547">
-        <v>0.95</v>
-      </c>
-      <c r="AA547">
-        <v>0.95</v>
-      </c>
-      <c r="AB547">
-        <v>0.95</v>
-      </c>
-      <c r="AC547">
-        <v>0.95</v>
-      </c>
-      <c r="AD547">
-        <v>0.95</v>
-      </c>
-      <c r="AE547">
-        <v>0.95</v>
-      </c>
-      <c r="AF547">
-        <v>0.95</v>
-      </c>
-      <c r="AG547">
-        <v>0.95</v>
-      </c>
-      <c r="AH547">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="548" spans="1:34">
-      <c r="A548">
-        <v>1</v>
-      </c>
-      <c r="B548" t="s">
-        <v>765</v>
-      </c>
-      <c r="C548" t="s">
-        <v>940</v>
-      </c>
-      <c r="D548" t="s">
-        <v>975</v>
-      </c>
-      <c r="E548" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F548" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G548">
-        <v>1</v>
-      </c>
-      <c r="H548">
-        <v>1</v>
-      </c>
-      <c r="I548">
-        <v>1</v>
-      </c>
-      <c r="J548">
-        <v>1</v>
-      </c>
-      <c r="K548">
-        <v>1</v>
-      </c>
-      <c r="L548">
-        <v>1</v>
-      </c>
-      <c r="M548">
-        <v>1</v>
-      </c>
-      <c r="N548">
-        <v>1</v>
-      </c>
-      <c r="O548">
-        <v>1</v>
-      </c>
-      <c r="P548">
-        <v>1</v>
-      </c>
-      <c r="Q548">
-        <v>1</v>
-      </c>
-      <c r="R548">
-        <v>1</v>
-      </c>
-      <c r="S548">
-        <v>1</v>
-      </c>
-      <c r="T548">
-        <v>1</v>
-      </c>
-      <c r="U548">
-        <v>1</v>
-      </c>
-      <c r="V548">
-        <v>1</v>
-      </c>
-      <c r="W548">
-        <v>1</v>
-      </c>
-      <c r="X548">
-        <v>1</v>
-      </c>
-      <c r="Y548">
-        <v>1</v>
-      </c>
-      <c r="Z548">
-        <v>1</v>
-      </c>
-      <c r="AA548">
-        <v>1</v>
-      </c>
-      <c r="AB548">
-        <v>1</v>
-      </c>
-      <c r="AC548">
-        <v>1</v>
-      </c>
-      <c r="AD548">
-        <v>1</v>
-      </c>
-      <c r="AE548">
-        <v>1</v>
-      </c>
-      <c r="AF548">
-        <v>1</v>
-      </c>
-      <c r="AG548">
-        <v>1</v>
-      </c>
-      <c r="AH548">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="549" spans="1:34">
-      <c r="A549">
-        <v>2</v>
-      </c>
-      <c r="B549" t="s">
-        <v>765</v>
-      </c>
-      <c r="C549" t="s">
-        <v>940</v>
-      </c>
-      <c r="D549" t="s">
-        <v>961</v>
-      </c>
-      <c r="E549" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F549" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G549">
-        <v>1</v>
-      </c>
-      <c r="H549">
-        <v>1</v>
-      </c>
-      <c r="I549">
-        <v>1</v>
-      </c>
-      <c r="J549">
-        <v>1</v>
-      </c>
-      <c r="K549">
-        <v>1</v>
-      </c>
-      <c r="L549">
-        <v>1</v>
-      </c>
-      <c r="M549">
-        <v>1</v>
-      </c>
-      <c r="N549">
-        <v>1</v>
-      </c>
-      <c r="O549">
-        <v>1</v>
-      </c>
-      <c r="P549">
-        <v>1</v>
-      </c>
-      <c r="Q549">
-        <v>1</v>
-      </c>
-      <c r="R549">
-        <v>1</v>
-      </c>
-      <c r="S549">
-        <v>1</v>
-      </c>
-      <c r="T549">
-        <v>1</v>
-      </c>
-      <c r="U549">
-        <v>1</v>
-      </c>
-      <c r="V549">
-        <v>1</v>
-      </c>
-      <c r="W549">
-        <v>1</v>
-      </c>
-      <c r="X549">
-        <v>1</v>
-      </c>
-      <c r="Y549">
-        <v>1</v>
-      </c>
-      <c r="Z549">
-        <v>1</v>
-      </c>
-      <c r="AA549">
-        <v>1</v>
-      </c>
-      <c r="AB549">
-        <v>1</v>
-      </c>
-      <c r="AC549">
-        <v>1</v>
-      </c>
-      <c r="AD549">
-        <v>1</v>
-      </c>
-      <c r="AE549">
-        <v>1</v>
-      </c>
-      <c r="AF549">
-        <v>1</v>
-      </c>
-      <c r="AG549">
-        <v>1</v>
-      </c>
-      <c r="AH549">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="550" spans="1:34">
-      <c r="A550">
-        <v>1</v>
-      </c>
-      <c r="B550" t="s">
-        <v>765</v>
-      </c>
-      <c r="C550" t="s">
-        <v>940</v>
-      </c>
-      <c r="D550" t="s">
-        <v>964</v>
-      </c>
-      <c r="E550" t="s">
-        <v>1004</v>
-      </c>
-      <c r="F550" t="s">
-        <v>590</v>
-      </c>
-      <c r="G550">
-        <v>0.95</v>
-      </c>
-      <c r="H550">
-        <v>0.95</v>
-      </c>
-      <c r="I550">
-        <v>0.95</v>
-      </c>
-      <c r="J550">
-        <v>0.95</v>
-      </c>
-      <c r="K550">
-        <v>0.95</v>
-      </c>
-      <c r="L550">
-        <v>0.95</v>
-      </c>
-      <c r="M550">
-        <v>0.95</v>
-      </c>
-      <c r="N550">
-        <v>0.95</v>
-      </c>
-      <c r="O550">
-        <v>0.95</v>
-      </c>
-      <c r="P550">
-        <v>0.95</v>
-      </c>
-      <c r="Q550">
-        <v>0.95</v>
-      </c>
-      <c r="R550">
-        <v>0.95</v>
-      </c>
-      <c r="S550">
-        <v>0.95</v>
-      </c>
-      <c r="T550">
-        <v>0.95</v>
-      </c>
-      <c r="U550">
-        <v>0.95</v>
-      </c>
-      <c r="V550">
-        <v>0.95</v>
-      </c>
-      <c r="W550">
-        <v>0.95</v>
-      </c>
-      <c r="X550">
-        <v>0.95</v>
-      </c>
-      <c r="Y550">
-        <v>0.95</v>
-      </c>
-      <c r="Z550">
-        <v>0.95</v>
-      </c>
-      <c r="AA550">
-        <v>0.95</v>
-      </c>
-      <c r="AB550">
-        <v>0.95</v>
-      </c>
-      <c r="AC550">
-        <v>0.95</v>
-      </c>
-      <c r="AD550">
-        <v>0.95</v>
-      </c>
-      <c r="AE550">
-        <v>0.95</v>
-      </c>
-      <c r="AF550">
-        <v>0.95</v>
-      </c>
-      <c r="AG550">
-        <v>0.95</v>
-      </c>
-      <c r="AH550">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="551" spans="1:34">
-      <c r="A551">
-        <v>2</v>
-      </c>
-      <c r="B551" t="s">
-        <v>765</v>
-      </c>
-      <c r="C551" t="s">
-        <v>940</v>
-      </c>
-      <c r="D551" t="s">
-        <v>976</v>
-      </c>
-      <c r="E551" t="s">
-        <v>1016</v>
-      </c>
-      <c r="F551" t="s">
-        <v>590</v>
-      </c>
-      <c r="G551">
-        <v>0.95</v>
-      </c>
-      <c r="H551">
-        <v>0.95</v>
-      </c>
-      <c r="I551">
-        <v>0.95</v>
-      </c>
-      <c r="J551">
-        <v>0.95</v>
-      </c>
-      <c r="K551">
-        <v>0.95</v>
-      </c>
-      <c r="L551">
-        <v>0.95</v>
-      </c>
-      <c r="M551">
-        <v>0.95</v>
-      </c>
-      <c r="N551">
-        <v>0.95</v>
-      </c>
-      <c r="O551">
-        <v>0.95</v>
-      </c>
-      <c r="P551">
-        <v>0.95</v>
-      </c>
-      <c r="Q551">
-        <v>0.95</v>
-      </c>
-      <c r="R551">
-        <v>0.95</v>
-      </c>
-      <c r="S551">
-        <v>0.95</v>
-      </c>
-      <c r="T551">
-        <v>0.95</v>
-      </c>
-      <c r="U551">
-        <v>0.95</v>
-      </c>
-      <c r="V551">
-        <v>0.95</v>
-      </c>
-      <c r="W551">
-        <v>0.95</v>
-      </c>
-      <c r="X551">
-        <v>0.95</v>
-      </c>
-      <c r="Y551">
-        <v>0.95</v>
-      </c>
-      <c r="Z551">
-        <v>0.95</v>
-      </c>
-      <c r="AA551">
-        <v>0.95</v>
-      </c>
-      <c r="AB551">
-        <v>0.95</v>
-      </c>
-      <c r="AC551">
-        <v>0.95</v>
-      </c>
-      <c r="AD551">
-        <v>0.95</v>
-      </c>
-      <c r="AE551">
-        <v>0.95</v>
-      </c>
-      <c r="AF551">
-        <v>0.95</v>
-      </c>
-      <c r="AG551">
-        <v>0.95</v>
-      </c>
-      <c r="AH551">
         <v>0.95</v>
       </c>
     </row>

--- a/t1_confection/A1_Outputs/A1_Outputs_B_Optimised_VRE/A-O_AR_Projections_COMPLETED.xlsx
+++ b/t1_confection/A1_Outputs/A1_Outputs_B_Optimised_VRE/A-O_AR_Projections_COMPLETED.xlsx
@@ -71261,88 +71261,88 @@
         <v>590</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH3">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="4" spans="1:34">
@@ -71469,88 +71469,88 @@
         <v>590</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH5">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="6" spans="1:34">
@@ -71677,88 +71677,88 @@
         <v>590</v>
       </c>
       <c r="G7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH7">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="8" spans="1:34">
@@ -71885,88 +71885,88 @@
         <v>590</v>
       </c>
       <c r="G9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH9">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="10" spans="1:34">
@@ -72093,88 +72093,88 @@
         <v>590</v>
       </c>
       <c r="G11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH11">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="12" spans="1:34">
@@ -72301,88 +72301,88 @@
         <v>590</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH13">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="14" spans="1:34">
@@ -72925,88 +72925,88 @@
         <v>590</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH19">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="20" spans="1:34">
@@ -73133,88 +73133,88 @@
         <v>590</v>
       </c>
       <c r="G21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH21">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="22" spans="1:34">
@@ -73341,88 +73341,88 @@
         <v>590</v>
       </c>
       <c r="G23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH23">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="24" spans="1:34">
@@ -73549,88 +73549,88 @@
         <v>590</v>
       </c>
       <c r="G25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH25">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="26" spans="1:34">
@@ -73757,88 +73757,88 @@
         <v>590</v>
       </c>
       <c r="G27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH27">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="28" spans="1:34">
@@ -73965,88 +73965,88 @@
         <v>590</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH29">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="30" spans="1:34">
@@ -74589,88 +74589,88 @@
         <v>590</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH35">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="36" spans="1:34">
@@ -74797,88 +74797,88 @@
         <v>590</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH37">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="38" spans="1:34">
@@ -75005,88 +75005,88 @@
         <v>590</v>
       </c>
       <c r="G39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH39">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="40" spans="1:34">
@@ -75213,88 +75213,88 @@
         <v>590</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH41">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="42" spans="1:34">
@@ -75421,88 +75421,88 @@
         <v>590</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH43">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="44" spans="1:34">
@@ -75629,88 +75629,88 @@
         <v>590</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH45">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="46" spans="1:34">
@@ -76253,88 +76253,88 @@
         <v>590</v>
       </c>
       <c r="G51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH51">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="52" spans="1:34">
@@ -76461,88 +76461,88 @@
         <v>590</v>
       </c>
       <c r="G53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH53">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="54" spans="1:34">
@@ -76669,88 +76669,88 @@
         <v>590</v>
       </c>
       <c r="G55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH55">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="56" spans="1:34">
@@ -76877,88 +76877,88 @@
         <v>590</v>
       </c>
       <c r="G57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH57">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="58" spans="1:34">
@@ -77085,88 +77085,88 @@
         <v>590</v>
       </c>
       <c r="G59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH59">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="60" spans="1:34">
@@ -77293,88 +77293,88 @@
         <v>590</v>
       </c>
       <c r="G61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH61">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="62" spans="1:34">
@@ -77917,88 +77917,88 @@
         <v>590</v>
       </c>
       <c r="G67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH67">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="68" spans="1:34">
@@ -78125,88 +78125,88 @@
         <v>590</v>
       </c>
       <c r="G69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH69">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="70" spans="1:34">
@@ -78333,88 +78333,88 @@
         <v>590</v>
       </c>
       <c r="G71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH71">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="72" spans="1:34">
@@ -78541,88 +78541,88 @@
         <v>590</v>
       </c>
       <c r="G73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH73">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="74" spans="1:34">
@@ -78749,88 +78749,88 @@
         <v>590</v>
       </c>
       <c r="G75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH75">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="76" spans="1:34">
@@ -78957,88 +78957,88 @@
         <v>590</v>
       </c>
       <c r="G77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH77">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="78" spans="1:34">
@@ -79581,88 +79581,88 @@
         <v>590</v>
       </c>
       <c r="G83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH83">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="84" spans="1:34">
@@ -79789,88 +79789,88 @@
         <v>590</v>
       </c>
       <c r="G85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH85">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="86" spans="1:34">
@@ -79997,88 +79997,88 @@
         <v>590</v>
       </c>
       <c r="G87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH87">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="88" spans="1:34">
@@ -80205,88 +80205,88 @@
         <v>590</v>
       </c>
       <c r="G89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH89">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="90" spans="1:34">
@@ -80413,88 +80413,88 @@
         <v>590</v>
       </c>
       <c r="G91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH91">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="92" spans="1:34">
@@ -80621,88 +80621,88 @@
         <v>590</v>
       </c>
       <c r="G93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH93">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="94" spans="1:34">
@@ -81245,88 +81245,88 @@
         <v>590</v>
       </c>
       <c r="G99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH99">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="100" spans="1:34">
@@ -81453,88 +81453,88 @@
         <v>590</v>
       </c>
       <c r="G101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH101">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="102" spans="1:34">
@@ -81661,88 +81661,88 @@
         <v>590</v>
       </c>
       <c r="G103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH103">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="104" spans="1:34">
@@ -81869,88 +81869,88 @@
         <v>590</v>
       </c>
       <c r="G105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH105">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="106" spans="1:34">
@@ -82077,88 +82077,88 @@
         <v>590</v>
       </c>
       <c r="G107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH107">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="108" spans="1:34">
@@ -82285,88 +82285,88 @@
         <v>590</v>
       </c>
       <c r="G109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH109">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="110" spans="1:34">
@@ -82909,88 +82909,88 @@
         <v>590</v>
       </c>
       <c r="G115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH115">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="116" spans="1:34">
@@ -83117,88 +83117,88 @@
         <v>590</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH117">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="118" spans="1:34">
@@ -83325,88 +83325,88 @@
         <v>590</v>
       </c>
       <c r="G119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH119">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="120" spans="1:34">
@@ -83533,88 +83533,88 @@
         <v>590</v>
       </c>
       <c r="G121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH121">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="122" spans="1:34">
@@ -83741,88 +83741,88 @@
         <v>590</v>
       </c>
       <c r="G123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH123">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="124" spans="1:34">
@@ -83949,88 +83949,88 @@
         <v>590</v>
       </c>
       <c r="G125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH125">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="126" spans="1:34">
@@ -84573,88 +84573,88 @@
         <v>590</v>
       </c>
       <c r="G131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH131">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="132" spans="1:34">
@@ -84781,88 +84781,88 @@
         <v>590</v>
       </c>
       <c r="G133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH133">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="134" spans="1:34">
@@ -84989,88 +84989,88 @@
         <v>590</v>
       </c>
       <c r="G135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH135">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="136" spans="1:34">
@@ -85197,88 +85197,88 @@
         <v>590</v>
       </c>
       <c r="G137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH137">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="138" spans="1:34">
@@ -85405,88 +85405,88 @@
         <v>590</v>
       </c>
       <c r="G139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH139">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="140" spans="1:34">
@@ -85613,88 +85613,88 @@
         <v>590</v>
       </c>
       <c r="G141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH141">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="142" spans="1:34">
@@ -86237,88 +86237,88 @@
         <v>590</v>
       </c>
       <c r="G147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH147">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="148" spans="1:34">
@@ -86445,88 +86445,88 @@
         <v>590</v>
       </c>
       <c r="G149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH149">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="150" spans="1:34">
@@ -86653,88 +86653,88 @@
         <v>590</v>
       </c>
       <c r="G151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH151">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="152" spans="1:34">
@@ -86861,88 +86861,88 @@
         <v>590</v>
       </c>
       <c r="G153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH153">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="154" spans="1:34">
@@ -87069,88 +87069,88 @@
         <v>590</v>
       </c>
       <c r="G155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH155">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="156" spans="1:34">
@@ -87277,88 +87277,88 @@
         <v>590</v>
       </c>
       <c r="G157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="H157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="I157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="J157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="K157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="L157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="M157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="N157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="O157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="P157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Q157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="R157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="S157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="T157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="U157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="V157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="W157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="X157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Y157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="Z157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AA157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AB157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AC157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AD157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AE157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AF157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AG157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
       <c r="AH157">
-        <v>1</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="158" spans="1:34">
